--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AB50BA-0500-420D-AF81-B466DE0653B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1946FD-3598-4681-BAAA-10722FA2AFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="1005" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2955" yWindow="825" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="189">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -739,6 +739,58 @@
   </si>
   <si>
     <t>siboribukuro_montblanc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>starch_syrup_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>wood_rod_great</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>opera_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>biscuit_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>brioche_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>huwakoro_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_chocolatetempering_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_bubblemist_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_mp_regenaration_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pan_cake_souffle_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>applepie_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>roll_cookie_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_statue_of_material_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3636,7 +3688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6706A2-EDB2-4593-B696-68963F977CA9}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -3713,7 +3765,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A26" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A27" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4500,6 +4552,39 @@
         <v>0</v>
       </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>1025</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>3000</v>
+      </c>
+      <c r="G27">
+        <v>1500</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>1</v>
       </c>
     </row>
@@ -6345,7 +6430,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DBDC14-7E25-4116-BA5C-8148F52CCF05}">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -6456,7 +6541,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" ref="A4:A66" si="0">ROW()-2+10000</f>
+        <f t="shared" ref="A4:A67" si="0">ROW()-2+10000</f>
         <v>10002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -8407,7 +8492,7 @@
         <v>10061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -8419,13 +8504,13 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G63">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
@@ -8440,7 +8525,7 @@
         <v>10062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -8452,13 +8537,13 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G64">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -8473,7 +8558,7 @@
         <v>10063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -8485,10 +8570,10 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G65">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -8506,7 +8591,7 @@
         <v>10064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -8524,7 +8609,7 @@
         <v>150</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -8535,11 +8620,11 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67">
-        <f t="shared" ref="A67:A76" si="1">ROW()-2+10000</f>
+        <f t="shared" si="0"/>
         <v>10065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -8551,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="G67">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -8568,11 +8653,11 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A68:A77" si="1">ROW()-2+10000</f>
         <v>10066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -8584,10 +8669,10 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="G68">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -8605,7 +8690,7 @@
         <v>10067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -8617,10 +8702,10 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G69">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -8638,7 +8723,7 @@
         <v>10068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -8650,10 +8735,10 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="G70">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -8671,7 +8756,7 @@
         <v>10069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -8683,10 +8768,10 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>3000</v>
+        <v>1300</v>
       </c>
       <c r="G71">
-        <v>1500</v>
+        <v>650</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -8704,7 +8789,7 @@
         <v>10070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -8716,10 +8801,10 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G72">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -8737,7 +8822,7 @@
         <v>10071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -8749,10 +8834,10 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="G73">
-        <v>750</v>
+        <v>5000</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -8770,7 +8855,7 @@
         <v>10072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -8782,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G74">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -8803,7 +8888,7 @@
         <v>10073</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -8836,30 +8921,63 @@
         <v>10074</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>500</v>
+      </c>
+      <c r="G76">
+        <v>250</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>10075</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
         <v>700</v>
       </c>
-      <c r="G76">
+      <c r="G77">
         <v>350</v>
       </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76">
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77">
         <v>1</v>
       </c>
     </row>
@@ -8872,7 +8990,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9247,11 +9365,11 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f t="shared" ref="A12:A16" si="2">ROW()-2+20000</f>
+        <f>ROW()-2+20000</f>
         <v>20010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -9263,10 +9381,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G12">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -9280,11 +9398,11 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" si="2"/>
+        <f>ROW()-2+20000</f>
         <v>20011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -9296,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="G13">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -9313,11 +9431,11 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="2"/>
+        <f>ROW()-2+20000</f>
         <v>20012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -9329,10 +9447,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="G14">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -9346,11 +9464,11 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="2"/>
+        <f>ROW()-2+20000</f>
         <v>20013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -9362,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="G15">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -9379,34 +9497,100 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="2"/>
+        <f>ROW()-2+20000</f>
         <v>20014</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>3000</v>
+      </c>
+      <c r="G16">
+        <v>1500</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f>ROW()-2+20000</f>
+        <v>20015</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>800</v>
       </c>
-      <c r="G16">
+      <c r="G17">
         <v>400</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16">
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f>ROW()-2+20000</f>
+        <v>20016</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>300</v>
+      </c>
+      <c r="G18">
+        <v>150</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
         <v>1</v>
       </c>
     </row>
@@ -9419,7 +9603,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9464,7 +9648,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A33" si="0">ROW()-2+30000</f>
+        <f>ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9497,7 +9681,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -9530,7 +9714,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -9563,7 +9747,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30003</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -9596,7 +9780,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -9629,7 +9813,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9662,7 +9846,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30006</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -9695,7 +9879,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -9728,7 +9912,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -9761,7 +9945,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -9794,7 +9978,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -9827,7 +10011,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -9849,7 +10033,7 @@
         <v>2500</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -9860,7 +10044,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -9893,7 +10077,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -9926,7 +10110,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -9959,7 +10143,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -9992,7 +10176,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -10025,7 +10209,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -10058,7 +10242,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -10091,7 +10275,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -10124,7 +10308,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -10157,7 +10341,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -10190,11 +10374,11 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -10223,7 +10407,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -10256,11 +10440,11 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -10272,10 +10456,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -10289,11 +10473,11 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -10305,10 +10489,10 @@
         <v>0</v>
       </c>
       <c r="F27">
+        <v>2000</v>
+      </c>
+      <c r="G27">
         <v>1000</v>
-      </c>
-      <c r="G27">
-        <v>500</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -10322,11 +10506,11 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -10338,10 +10522,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="G28">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -10355,11 +10539,11 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10371,13 +10555,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="G29">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -10388,11 +10572,11 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10404,13 +10588,13 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="G30">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -10421,11 +10605,11 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10437,10 +10621,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G31">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -10454,11 +10638,11 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10470,10 +10654,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="G32">
-        <v>250</v>
+        <v>10000</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -10487,34 +10671,166 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>500</v>
+      </c>
+      <c r="G33">
+        <v>250</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <f>ROW()-2+30000</f>
+        <v>30032</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>500</v>
+      </c>
+      <c r="G34">
+        <v>250</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <f>ROW()-2+30000</f>
+        <v>30033</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
         <v>700</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <v>350</v>
       </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <f>ROW()-2+30000</f>
+        <v>30034</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>5000</v>
+      </c>
+      <c r="G36">
+        <v>2500</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <f>ROW()-2+30000</f>
+        <v>30035</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>2800</v>
+      </c>
+      <c r="G37">
+        <v>1400</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37">
         <v>1</v>
       </c>
     </row>
@@ -10527,7 +10843,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4060CA39-02FB-4508-8603-5A906A5C9777}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -10572,7 +10888,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A14" si="0">ROW()-2+40000</f>
+        <f t="shared" ref="A2:A18" si="0">ROW()-2+40000</f>
         <v>40000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -10654,10 +10970,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="G4">
-        <v>7500</v>
+        <v>12500</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -10726,7 +11042,7 @@
         <v>750</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -10759,7 +11075,7 @@
         <v>10000</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -10792,7 +11108,7 @@
         <v>25000</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -10807,22 +11123,22 @@
         <v>40007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="G9">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -10840,7 +11156,7 @@
         <v>40008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -10852,13 +11168,13 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>8000</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>4000</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -10873,7 +11189,7 @@
         <v>40009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -10885,10 +11201,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>5000</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -10906,7 +11222,7 @@
         <v>40010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -10939,7 +11255,7 @@
         <v>40011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -10951,10 +11267,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G13">
-        <v>3750</v>
+        <v>2500</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -10972,22 +11288,22 @@
         <v>40012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>7500</v>
       </c>
       <c r="G14">
-        <v>50</v>
+        <v>3750</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -11001,11 +11317,11 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" ref="A15:A16" si="1">ROW()-2+40000</f>
+        <f t="shared" si="0"/>
         <v>40013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -11017,13 +11333,13 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="G15">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -11034,34 +11350,199 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
+        <f t="shared" si="0"/>
+        <v>40014</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>800</v>
+      </c>
+      <c r="G16">
+        <v>400</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>40015</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1200</v>
+      </c>
+      <c r="G17">
+        <v>600</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>40016</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
+        <v>50</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f t="shared" ref="A19:A21" si="1">ROW()-2+40000</f>
+        <v>40017</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>500</v>
+      </c>
+      <c r="G19">
+        <v>250</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20">
         <f t="shared" si="1"/>
-        <v>40014</v>
-      </c>
-      <c r="B16" s="1" t="s">
+        <v>40018</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>700</v>
       </c>
-      <c r="G16">
+      <c r="G20">
         <v>350</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16">
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f t="shared" si="1"/>
+        <v>40019</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>5000</v>
+      </c>
+      <c r="G21">
+        <v>2500</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1946FD-3598-4681-BAAA-10722FA2AFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E7608A-A19C-4AA6-BDC0-4B3799A73E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="825" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="1095" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -4573,10 +4573,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G27">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -9365,7 +9365,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f>ROW()-2+20000</f>
+        <f t="shared" ref="A12:A18" si="2">ROW()-2+20000</f>
         <v>20010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f>ROW()-2+20000</f>
+        <f t="shared" si="2"/>
         <v>20011</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -9431,7 +9431,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f>ROW()-2+20000</f>
+        <f t="shared" si="2"/>
         <v>20012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -9464,7 +9464,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f>ROW()-2+20000</f>
+        <f t="shared" si="2"/>
         <v>20013</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -9497,7 +9497,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f>ROW()-2+20000</f>
+        <f t="shared" si="2"/>
         <v>20014</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -9530,7 +9530,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f>ROW()-2+20000</f>
+        <f t="shared" si="2"/>
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -9563,7 +9563,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f>ROW()-2+20000</f>
+        <f t="shared" si="2"/>
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -9648,7 +9648,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>ROW()-2+30000</f>
+        <f t="shared" ref="A2:A37" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9681,7 +9681,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -9714,7 +9714,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -9747,7 +9747,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30003</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -9780,7 +9780,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -9813,7 +9813,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9846,7 +9846,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30006</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -9879,7 +9879,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -9912,7 +9912,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -9945,7 +9945,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -9978,7 +9978,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -10011,7 +10011,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10044,7 +10044,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -10077,7 +10077,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10110,7 +10110,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -10143,7 +10143,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -10176,7 +10176,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -10209,7 +10209,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -10242,7 +10242,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -10275,7 +10275,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -10308,7 +10308,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -10341,7 +10341,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -10374,7 +10374,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -10407,7 +10407,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -10440,7 +10440,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -10473,7 +10473,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -10506,7 +10506,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -10539,7 +10539,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -10572,7 +10572,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -10605,7 +10605,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -10638,7 +10638,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -10671,7 +10671,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -10704,7 +10704,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -10737,7 +10737,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30033</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -10770,7 +10770,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30034</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -10803,7 +10803,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30035</v>
       </c>
       <c r="B37" s="1" t="s">

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E7608A-A19C-4AA6-BDC0-4B3799A73E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E14D6D-EFF4-464A-8112-2738DEB70636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="1095" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1230" yWindow="1050" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="190">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -791,6 +791,10 @@
   </si>
   <si>
     <t>mg_statue_of_material_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_bake_beans_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9603,7 +9607,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9648,7 +9652,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A37" si="0">ROW()-2+30000</f>
+        <f t="shared" ref="A2:A38" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -10555,10 +10559,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="G29">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -10774,7 +10778,7 @@
         <v>30034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -10786,10 +10790,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="G36">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -10798,7 +10802,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -10807,30 +10811,63 @@
         <v>30035</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>3000</v>
+      </c>
+      <c r="G37">
+        <v>1500</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>30036</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
         <v>2800</v>
       </c>
-      <c r="G37">
+      <c r="G38">
         <v>1400</v>
       </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37">
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E14D6D-EFF4-464A-8112-2738DEB70636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7E51EE-09B9-44E3-9930-B262D7A847AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="1050" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="840" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="191">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -795,6 +795,10 @@
   </si>
   <si>
     <t>mg_bake_beans_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>himawari_seed</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3692,7 +3696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6706A2-EDB2-4593-B696-68963F977CA9}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -3769,7 +3773,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A27" si="0">ROW()-2+1000</f>
+        <f t="shared" ref="A3:A28" si="0">ROW()-2+1000</f>
         <v>1001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4037,7 +4041,7 @@
         <v>1009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C11">
         <v>50</v>
@@ -4049,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -4070,7 +4074,7 @@
         <v>1010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -4082,10 +4086,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -4103,7 +4107,7 @@
         <v>1011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -4115,10 +4119,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="G13">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -4136,7 +4140,7 @@
         <v>1012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -4148,10 +4152,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -4169,7 +4173,7 @@
         <v>1013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>50</v>
@@ -4181,13 +4185,13 @@
         <v>0</v>
       </c>
       <c r="F15">
+        <v>40</v>
+      </c>
+      <c r="G15">
         <v>20</v>
       </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -4202,7 +4206,7 @@
         <v>1014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>50</v>
@@ -4214,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -4235,25 +4239,25 @@
         <v>1015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>50</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -4268,22 +4272,22 @@
         <v>1016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G18">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -4301,7 +4305,7 @@
         <v>1017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -4313,10 +4317,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="G19">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -4334,7 +4338,7 @@
         <v>1018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -4346,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G20">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -4367,22 +4371,22 @@
         <v>1019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -4400,7 +4404,7 @@
         <v>1020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -4412,13 +4416,13 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G22">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -4433,7 +4437,7 @@
         <v>1021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -4445,13 +4449,13 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="G23">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -4466,22 +4470,22 @@
         <v>1022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -4499,7 +4503,7 @@
         <v>1023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -4511,10 +4515,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G25">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -4532,7 +4536,7 @@
         <v>1024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -4544,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G26">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -4565,30 +4569,63 @@
         <v>1025</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>500</v>
+      </c>
+      <c r="G27">
+        <v>250</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>1026</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>20000</v>
       </c>
-      <c r="G27">
+      <c r="G28">
         <v>10000</v>
       </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28">
         <v>1</v>
       </c>
     </row>
@@ -8994,7 +9031,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9369,7 +9406,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f t="shared" ref="A12:A18" si="2">ROW()-2+20000</f>
+        <f t="shared" ref="A12:A19" si="2">ROW()-2+20000</f>
         <v>20010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -9571,30 +9608,63 @@
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>500</v>
+      </c>
+      <c r="G18">
+        <v>250</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f t="shared" si="2"/>
+        <v>20017</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>300</v>
       </c>
-      <c r="G18">
+      <c r="G19">
         <v>150</v>
       </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18">
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
         <v>1</v>
       </c>
     </row>
@@ -10697,7 +10767,7 @@
         <v>250</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7E51EE-09B9-44E3-9930-B262D7A847AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0389021C-1ED7-4CE9-93BB-B7A8494B3EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="840" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="191">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -9031,7 +9031,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9076,7 +9076,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A4" si="0">ROW()-2+20000</f>
+        <f t="shared" ref="A2:A6" si="0">ROW()-2+20000</f>
         <v>20000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9175,11 +9175,11 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f t="shared" ref="A5:A11" si="1">ROW()-2+20000</f>
+        <f t="shared" si="0"/>
         <v>20003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -9194,7 +9194,7 @@
         <v>30</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -9208,11 +9208,11 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -9224,10 +9224,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -9241,17 +9241,17 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A7:A13" si="1">ROW()-2+20000</f>
         <v>20005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C7">
         <v>50</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -9260,7 +9260,7 @@
         <v>30</v>
       </c>
       <c r="G7">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -9278,7 +9278,7 @@
         <v>20006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -9290,10 +9290,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -9311,25 +9311,25 @@
         <v>20007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2300</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -9344,22 +9344,22 @@
         <v>20008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1500</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -9377,25 +9377,25 @@
         <v>20009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>3000</v>
+        <v>2300</v>
       </c>
       <c r="G11">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -9406,26 +9406,26 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f t="shared" ref="A12:A19" si="2">ROW()-2+20000</f>
+        <f t="shared" si="1"/>
         <v>20010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="G12">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -9439,23 +9439,23 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G13">
         <v>250</v>
@@ -9472,11 +9472,11 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A14:A21" si="2">ROW()-2+20000</f>
         <v>20012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -9488,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="G14">
-        <v>650</v>
+        <v>200</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -9509,7 +9509,7 @@
         <v>20013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -9521,10 +9521,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G15">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -9542,7 +9542,7 @@
         <v>20014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -9554,10 +9554,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>3000</v>
+        <v>1300</v>
       </c>
       <c r="G16">
-        <v>1500</v>
+        <v>650</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -9575,7 +9575,7 @@
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -9587,10 +9587,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G17">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -9608,7 +9608,7 @@
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -9620,10 +9620,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G18">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -9641,30 +9641,96 @@
         <v>20017</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>800</v>
+      </c>
+      <c r="G19">
+        <v>400</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f t="shared" si="2"/>
+        <v>20018</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>500</v>
+      </c>
+      <c r="G20">
+        <v>250</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f t="shared" si="2"/>
+        <v>20019</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>300</v>
       </c>
-      <c r="G19">
+      <c r="G21">
         <v>150</v>
       </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19">
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0389021C-1ED7-4CE9-93BB-B7A8494B3EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5800DF0-60AF-4A9B-AC3F-114B30704A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2115" yWindow="960" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="192">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -799,6 +799,10 @@
   </si>
   <si>
     <t>himawari_seed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>coffee_mill</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9743,7 +9747,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9788,7 +9792,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A38" si="0">ROW()-2+30000</f>
+        <f t="shared" ref="A2:A39" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -10200,13 +10204,13 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -10239,7 +10243,7 @@
         <v>150</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -10320,7 +10324,7 @@
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -10332,10 +10336,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="G18">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -10353,7 +10357,7 @@
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -10386,7 +10390,7 @@
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -10398,10 +10402,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="G20">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -10419,25 +10423,25 @@
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="G21">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -10452,7 +10456,7 @@
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -10464,10 +10468,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -10485,7 +10489,7 @@
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -10497,13 +10501,13 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G23">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -10518,7 +10522,7 @@
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>179</v>
+        <v>68</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -10530,10 +10534,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G24">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -10551,7 +10555,7 @@
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -10563,10 +10567,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -10584,7 +10588,7 @@
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>176</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -10596,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G26">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -10617,7 +10621,7 @@
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -10629,10 +10633,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -10650,7 +10654,7 @@
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -10662,10 +10666,10 @@
         <v>0</v>
       </c>
       <c r="F28">
+        <v>2000</v>
+      </c>
+      <c r="G28">
         <v>1000</v>
-      </c>
-      <c r="G28">
-        <v>500</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -10683,7 +10687,7 @@
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10695,10 +10699,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="G29">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -10716,7 +10720,7 @@
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10728,13 +10732,13 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="G30">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -10749,7 +10753,7 @@
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10761,13 +10765,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="G31">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -10782,7 +10786,7 @@
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10794,10 +10798,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="G32">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -10815,7 +10819,7 @@
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10827,13 +10831,13 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="G33">
-        <v>250</v>
+        <v>10000</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -10848,7 +10852,7 @@
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -10866,7 +10870,7 @@
         <v>250</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -10881,7 +10885,7 @@
         <v>30033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -10893,10 +10897,10 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G35">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -10914,7 +10918,7 @@
         <v>30034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -10926,10 +10930,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G36">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -10947,7 +10951,7 @@
         <v>30035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -10959,10 +10963,10 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G37">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -10980,30 +10984,63 @@
         <v>30036</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>3000</v>
+      </c>
+      <c r="G38">
+        <v>1500</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>30037</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
         <v>2800</v>
       </c>
-      <c r="G38">
+      <c r="G39">
         <v>1400</v>
       </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38">
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39">
         <v>1</v>
       </c>
     </row>
@@ -11016,7 +11053,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4060CA39-02FB-4508-8603-5A906A5C9777}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11061,7 +11098,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A18" si="0">ROW()-2+40000</f>
+        <f t="shared" ref="A2:A17" si="0">ROW()-2+40000</f>
         <v>40000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -11308,10 +11345,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="G9">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -11589,11 +11626,11 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A18" si="1">ROW()-2+40000</f>
         <v>40016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -11605,117 +11642,18 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="G18">
-        <v>50</v>
+        <v>2500</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <f t="shared" ref="A19:A21" si="1">ROW()-2+40000</f>
-        <v>40017</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>500</v>
-      </c>
-      <c r="G19">
-        <v>250</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <f t="shared" si="1"/>
-        <v>40018</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>700</v>
-      </c>
-      <c r="G20">
-        <v>350</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <f t="shared" si="1"/>
-        <v>40019</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>5000</v>
-      </c>
-      <c r="G21">
-        <v>2500</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5800DF0-60AF-4A9B-AC3F-114B30704A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA12FAFE-8E21-4EE6-980F-A8959CF3AD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="960" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="193">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -803,6 +803,10 @@
   </si>
   <si>
     <t>coffee_mill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>flyer</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8885,7 +8889,7 @@
         <v>5000</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -9747,7 +9751,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9792,7 +9796,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A39" si="0">ROW()-2+30000</f>
+        <f t="shared" ref="A2:A40" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -10270,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="G16">
         <v>750</v>
@@ -10456,25 +10460,25 @@
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>150</v>
+        <v>3000</v>
       </c>
       <c r="G22">
-        <v>75</v>
+        <v>1500</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -10489,7 +10493,7 @@
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -10501,10 +10505,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -10522,7 +10526,7 @@
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -10534,13 +10538,13 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G24">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -10555,7 +10559,7 @@
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>179</v>
+        <v>68</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -10567,10 +10571,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G25">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -10588,7 +10592,7 @@
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -10600,10 +10604,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G26">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -10621,7 +10625,7 @@
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>176</v>
+        <v>107</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -10633,10 +10637,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G27">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -10654,7 +10658,7 @@
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -10666,10 +10670,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -10687,7 +10691,7 @@
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10699,10 +10703,10 @@
         <v>0</v>
       </c>
       <c r="F29">
+        <v>2000</v>
+      </c>
+      <c r="G29">
         <v>1000</v>
-      </c>
-      <c r="G29">
-        <v>500</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -10720,7 +10724,7 @@
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10732,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="G30">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -10753,7 +10757,7 @@
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10765,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="G31">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -10786,7 +10790,7 @@
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10798,13 +10802,13 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="G32">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -10819,7 +10823,7 @@
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10831,10 +10835,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="G33">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -10852,7 +10856,7 @@
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -10864,13 +10868,13 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="G34">
-        <v>250</v>
+        <v>10000</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -10885,7 +10889,7 @@
         <v>30033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -10903,7 +10907,7 @@
         <v>250</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -10918,7 +10922,7 @@
         <v>30034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -10930,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G36">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -10951,7 +10955,7 @@
         <v>30035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -10963,10 +10967,10 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G37">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -10984,7 +10988,7 @@
         <v>30036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -10996,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G38">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -11017,30 +11021,63 @@
         <v>30037</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>3000</v>
+      </c>
+      <c r="G39">
+        <v>1500</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>30038</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>2800</v>
       </c>
-      <c r="G39">
+      <c r="G40">
         <v>1400</v>
       </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39">
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA12FAFE-8E21-4EE6-980F-A8959CF3AD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC0AAAC-E4DB-45BD-8A3C-BEB647435F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="193">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -9039,7 +9039,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9249,7 +9249,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" ref="A7:A13" si="1">ROW()-2+20000</f>
+        <f t="shared" ref="A7:A14" si="1">ROW()-2+20000</f>
         <v>20005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9451,19 +9451,19 @@
         <v>20011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G13">
         <v>250</v>
@@ -9480,26 +9480,26 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" ref="A14:A21" si="2">ROW()-2+20000</f>
+        <f t="shared" si="1"/>
         <v>20012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="G14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -9513,11 +9513,11 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A15:A22" si="2">ROW()-2+20000</f>
         <v>20013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -9529,10 +9529,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G15">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -9550,7 +9550,7 @@
         <v>20014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="G16">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -9583,7 +9583,7 @@
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -9595,10 +9595,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="G17">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -9616,7 +9616,7 @@
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -9628,10 +9628,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="G18">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -9649,7 +9649,7 @@
         <v>20017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -9661,10 +9661,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="G19">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -9682,7 +9682,7 @@
         <v>20018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -9694,10 +9694,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G20">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -9715,30 +9715,63 @@
         <v>20019</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>500</v>
+      </c>
+      <c r="G21">
+        <v>250</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <f t="shared" si="2"/>
+        <v>20020</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>300</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>150</v>
       </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <v>1</v>
       </c>
     </row>
@@ -10214,7 +10247,7 @@
         <v>250</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC0AAAC-E4DB-45BD-8A3C-BEB647435F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C563C8FE-79F4-45B0-8CEF-96F50B88147D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="194">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -807,6 +807,10 @@
   </si>
   <si>
     <t>flyer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>donuts_recipi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6479,7 +6483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DBDC14-7E25-4116-BA5C-8148F52CCF05}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -6590,7 +6594,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" ref="A4:A67" si="0">ROW()-2+10000</f>
+        <f t="shared" ref="A4:A68" si="0">ROW()-2+10000</f>
         <v>10002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -7749,7 +7753,7 @@
         <v>10037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>101</v>
+        <v>192</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -7761,13 +7765,13 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="G39">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -7782,7 +7786,7 @@
         <v>10038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -7794,10 +7798,10 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="G40">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -7815,7 +7819,7 @@
         <v>10039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -7827,10 +7831,10 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G41">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -7848,7 +7852,7 @@
         <v>10040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -7860,10 +7864,10 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="G42">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -7881,7 +7885,7 @@
         <v>10041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -7893,10 +7897,10 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="G43">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -7914,25 +7918,25 @@
         <v>10042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>500</v>
+        <v>50000</v>
       </c>
       <c r="G44">
-        <v>250</v>
+        <v>25000</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -7947,7 +7951,7 @@
         <v>10043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -7959,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G45">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -7980,7 +7984,7 @@
         <v>10044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -7992,10 +7996,10 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G46">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -8013,7 +8017,7 @@
         <v>10045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -8025,13 +8029,13 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="G47">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -8046,7 +8050,7 @@
         <v>10046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -8058,13 +8062,13 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="G48">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -8079,7 +8083,7 @@
         <v>10047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -8091,10 +8095,10 @@
         <v>0</v>
       </c>
       <c r="F49">
+        <v>3000</v>
+      </c>
+      <c r="G49">
         <v>1500</v>
-      </c>
-      <c r="G49">
-        <v>750</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -8112,7 +8116,7 @@
         <v>10048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -8124,13 +8128,13 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>750</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -8145,7 +8149,7 @@
         <v>10049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -8157,13 +8161,13 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>5000</v>
+        <v>10</v>
       </c>
       <c r="G51">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>2000</v>
+        <v>4</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -8178,7 +8182,7 @@
         <v>10050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -8196,7 +8200,7 @@
         <v>2500</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -8211,7 +8215,7 @@
         <v>10051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -8223,10 +8227,10 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G53">
-        <v>3750</v>
+        <v>2500</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -8244,25 +8248,25 @@
         <v>10052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>100</v>
+        <v>7500</v>
       </c>
       <c r="G54">
-        <v>50</v>
+        <v>3750</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -8277,7 +8281,7 @@
         <v>10053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -8289,10 +8293,10 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G55">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -8310,7 +8314,7 @@
         <v>10054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -8322,10 +8326,10 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G56">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -8343,7 +8347,7 @@
         <v>10055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -8355,13 +8359,13 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G57">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -8376,7 +8380,7 @@
         <v>10056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -8388,13 +8392,13 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="G58">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -8409,7 +8413,7 @@
         <v>10057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -8421,10 +8425,10 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G59">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -8442,7 +8446,7 @@
         <v>10058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -8454,10 +8458,10 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G60">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -8475,7 +8479,7 @@
         <v>10059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -8487,13 +8491,13 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="G61">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -8508,7 +8512,7 @@
         <v>10060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -8526,7 +8530,7 @@
         <v>150</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -8541,7 +8545,7 @@
         <v>10061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -8553,10 +8557,10 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G63">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -8574,7 +8578,7 @@
         <v>10062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -8586,13 +8590,13 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G64">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -8607,7 +8611,7 @@
         <v>10063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -8619,13 +8623,13 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G65">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -8640,7 +8644,7 @@
         <v>10064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -8652,10 +8656,10 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G66">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -8673,7 +8677,7 @@
         <v>10065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -8691,7 +8695,7 @@
         <v>150</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -8702,11 +8706,11 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
-        <f t="shared" ref="A68:A77" si="1">ROW()-2+10000</f>
+        <f t="shared" si="0"/>
         <v>10066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -8718,13 +8722,13 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="G68">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -8735,11 +8739,11 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A69:A73" si="1">ROW()-2+10000</f>
         <v>10067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -8751,13 +8755,13 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="G69">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -8772,7 +8776,7 @@
         <v>10068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -8784,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G70">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -8805,7 +8809,7 @@
         <v>10069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -8817,10 +8821,10 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="G71">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -8838,7 +8842,7 @@
         <v>10070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -8850,10 +8854,10 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G72">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -8871,7 +8875,7 @@
         <v>10071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -8883,150 +8887,18 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="G73">
-        <v>5000</v>
+        <v>350</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
       </c>
       <c r="J73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <f t="shared" si="1"/>
-        <v>10072</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C74">
-        <v>1</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74">
-        <v>1500</v>
-      </c>
-      <c r="G74">
-        <v>750</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <f t="shared" si="1"/>
-        <v>10073</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75">
-        <v>500</v>
-      </c>
-      <c r="G75">
-        <v>250</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <f t="shared" si="1"/>
-        <v>10074</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <v>500</v>
-      </c>
-      <c r="G76">
-        <v>250</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <f t="shared" si="1"/>
-        <v>10075</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77">
-        <v>700</v>
-      </c>
-      <c r="G77">
-        <v>350</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77">
         <v>1</v>
       </c>
     </row>
@@ -9784,7 +9656,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9829,7 +9701,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A40" si="0">ROW()-2+30000</f>
+        <f>ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9862,7 +9734,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -9895,7 +9767,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -9928,7 +9800,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30003</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -9961,7 +9833,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -9994,7 +9866,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -10027,7 +9899,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30006</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -10060,7 +9932,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -10093,7 +9965,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -10126,7 +9998,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -10159,7 +10031,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -10192,7 +10064,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10225,7 +10097,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -10258,7 +10130,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10291,7 +10163,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -10324,7 +10196,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -10357,7 +10229,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -10390,7 +10262,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -10423,7 +10295,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -10456,7 +10328,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -10489,29 +10361,29 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>3000</v>
+        <v>150</v>
       </c>
       <c r="G22">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -10522,11 +10394,11 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -10538,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G23">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -10555,11 +10427,11 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -10571,13 +10443,13 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -10588,11 +10460,11 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>179</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -10604,10 +10476,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -10621,11 +10493,11 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -10637,10 +10509,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G26">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -10654,11 +10526,11 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -10670,10 +10542,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="G27">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -10687,11 +10559,11 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -10703,10 +10575,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="G28">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -10720,11 +10592,11 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10736,10 +10608,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -10753,11 +10625,11 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10769,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="G30">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -10786,11 +10658,11 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10802,13 +10674,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="G31">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -10819,11 +10691,11 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10835,13 +10707,13 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G32">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -10852,11 +10724,11 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10868,10 +10740,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G33">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -10885,11 +10757,11 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -10901,13 +10773,13 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>20000</v>
+        <v>500</v>
       </c>
       <c r="G34">
-        <v>10000</v>
+        <v>250</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -10918,11 +10790,11 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -10940,7 +10812,7 @@
         <v>250</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -10951,11 +10823,11 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -10967,10 +10839,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G36">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -10984,11 +10856,11 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -11000,10 +10872,10 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G37">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -11017,11 +10889,11 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -11033,10 +10905,10 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G38">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -11050,11 +10922,11 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -11066,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="G39">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -11078,39 +10950,6 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <f t="shared" si="0"/>
-        <v>30038</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>2800</v>
-      </c>
-      <c r="G40">
-        <v>1400</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C563C8FE-79F4-45B0-8CEF-96F50B88147D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A190382-7F52-4E25-BA72-651E06076968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -8002,7 +8002,7 @@
         <v>500</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -8035,7 +8035,7 @@
         <v>400</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -9701,7 +9701,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>ROW()-2+30000</f>
+        <f t="shared" ref="A2:A39" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9734,7 +9734,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -9767,7 +9767,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -9800,7 +9800,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30003</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -9833,7 +9833,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -9866,7 +9866,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9899,7 +9899,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30006</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -9932,7 +9932,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -9965,7 +9965,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -9998,7 +9998,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -10031,7 +10031,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -10064,7 +10064,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10097,7 +10097,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -10130,7 +10130,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10163,7 +10163,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -10196,7 +10196,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -10229,7 +10229,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -10262,7 +10262,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -10295,7 +10295,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -10328,7 +10328,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -10361,7 +10361,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -10394,7 +10394,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -10427,7 +10427,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -10460,7 +10460,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -10493,7 +10493,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -10526,7 +10526,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -10559,7 +10559,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -10592,7 +10592,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -10625,7 +10625,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -10658,7 +10658,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -10691,7 +10691,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -10724,7 +10724,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -10757,7 +10757,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -10790,7 +10790,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30033</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -10823,7 +10823,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30034</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -10856,7 +10856,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30035</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -10889,7 +10889,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30036</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -10922,7 +10922,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30037</v>
       </c>
       <c r="B39" s="1" t="s">

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A190382-7F52-4E25-BA72-651E06076968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD0F2DF-0299-4C2A-B4DA-D29D3E7C05C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="194">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -6483,7 +6483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DBDC14-7E25-4116-BA5C-8148F52CCF05}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -6594,7 +6594,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" ref="A4:A68" si="0">ROW()-2+10000</f>
+        <f t="shared" ref="A4:A67" si="0">ROW()-2+10000</f>
         <v>10002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -8512,7 +8512,7 @@
         <v>10060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -8530,7 +8530,7 @@
         <v>150</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -8545,7 +8545,7 @@
         <v>10061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -8557,10 +8557,10 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G63">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -8578,7 +8578,7 @@
         <v>10062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -8590,13 +8590,13 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G64">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -8611,7 +8611,7 @@
         <v>10063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -8623,13 +8623,13 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G65">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>10064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -8656,10 +8656,10 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G66">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -8677,7 +8677,7 @@
         <v>10065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -8689,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="F67">
+        <v>600</v>
+      </c>
+      <c r="G67">
         <v>300</v>
-      </c>
-      <c r="G67">
-        <v>150</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -8706,11 +8706,11 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A68:A69" si="1">ROW()-2+10000</f>
         <v>10066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>193</v>
+        <v>27</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -8722,10 +8722,10 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>600</v>
+        <v>10000</v>
       </c>
       <c r="G68">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -8739,11 +8739,11 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69">
-        <f t="shared" ref="A69:A73" si="1">ROW()-2+10000</f>
+        <f t="shared" si="1"/>
         <v>10067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -8755,150 +8755,18 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>10000</v>
+        <v>700</v>
       </c>
       <c r="G69">
-        <v>5000</v>
+        <v>350</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
       </c>
       <c r="J69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <f t="shared" si="1"/>
-        <v>10068</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70">
-        <v>1500</v>
-      </c>
-      <c r="G70">
-        <v>750</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <f t="shared" si="1"/>
-        <v>10069</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <v>500</v>
-      </c>
-      <c r="G71">
-        <v>250</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <f t="shared" si="1"/>
-        <v>10070</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72">
-        <v>500</v>
-      </c>
-      <c r="G72">
-        <v>250</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <f t="shared" si="1"/>
-        <v>10071</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
-      <c r="F73">
-        <v>700</v>
-      </c>
-      <c r="G73">
-        <v>350</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73">
         <v>1</v>
       </c>
     </row>
@@ -8911,7 +8779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -8978,7 +8846,7 @@
         <v>15</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -9044,7 +8912,7 @@
         <v>35</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -9121,7 +8989,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" ref="A7:A14" si="1">ROW()-2+20000</f>
+        <f t="shared" ref="A7:A15" si="1">ROW()-2+20000</f>
         <v>20005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9356,19 +9224,19 @@
         <v>20012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G14">
         <v>250</v>
@@ -9385,26 +9253,26 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" ref="A15:A22" si="2">ROW()-2+20000</f>
+        <f t="shared" si="1"/>
         <v>20013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="G15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -9418,11 +9286,11 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A16:A27" si="2">ROW()-2+20000</f>
         <v>20014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -9434,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G16">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -9455,7 +9323,7 @@
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -9467,10 +9335,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="G17">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -9488,7 +9356,7 @@
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -9500,10 +9368,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="G18">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -9521,7 +9389,7 @@
         <v>20017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -9533,10 +9401,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="G19">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -9554,7 +9422,7 @@
         <v>20018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -9566,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="G20">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -9587,7 +9455,7 @@
         <v>20019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -9599,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G21">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -9644,6 +9512,171 @@
         <v>0</v>
       </c>
       <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <f t="shared" si="2"/>
+        <v>20021</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>500</v>
+      </c>
+      <c r="G23">
+        <v>250</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <f t="shared" si="2"/>
+        <v>20022</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>800</v>
+      </c>
+      <c r="G24">
+        <v>400</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <f t="shared" si="2"/>
+        <v>20023</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>4000</v>
+      </c>
+      <c r="G25">
+        <v>2000</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <f t="shared" si="2"/>
+        <v>20024</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>500</v>
+      </c>
+      <c r="G26">
+        <v>250</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f t="shared" si="2"/>
+        <v>20025</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>3000</v>
+      </c>
+      <c r="G27">
+        <v>1500</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>1</v>
       </c>
     </row>
@@ -9656,7 +9689,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9701,11 +9734,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A39" si="0">ROW()-2+30000</f>
+        <f t="shared" ref="A2:A35" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -9717,10 +9750,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -9738,7 +9771,7 @@
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -9750,13 +9783,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>10</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -9771,7 +9804,7 @@
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>50</v>
@@ -9783,13 +9816,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -9804,7 +9837,7 @@
         <v>30003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -9816,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -9837,7 +9870,7 @@
         <v>30004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -9852,7 +9885,7 @@
         <v>30</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -9870,7 +9903,7 @@
         <v>30005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -9882,10 +9915,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -9903,7 +9936,7 @@
         <v>30006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -9915,10 +9948,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1200</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>15</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -9936,22 +9969,22 @@
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>50</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -9969,22 +10002,22 @@
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="C10">
         <v>50</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="G10">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -10002,7 +10035,7 @@
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="C11">
         <v>50</v>
@@ -10014,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>50</v>
@@ -10035,22 +10068,22 @@
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -10068,25 +10101,25 @@
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>15000</v>
+        <v>50</v>
       </c>
       <c r="G13">
-        <v>2500</v>
+        <v>50</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -10101,7 +10134,7 @@
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -10113,13 +10146,13 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G14">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -10134,7 +10167,7 @@
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -10146,13 +10179,13 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>300</v>
+        <v>15000</v>
       </c>
       <c r="G15">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -10167,7 +10200,7 @@
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -10179,10 +10212,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="G16">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -10200,7 +10233,7 @@
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -10212,10 +10245,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G17">
-        <v>250</v>
+        <v>750</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -10530,7 +10563,7 @@
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -10542,10 +10575,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="G27">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -10563,7 +10596,7 @@
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -10575,10 +10608,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -10596,7 +10629,7 @@
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10608,13 +10641,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G29">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -10629,7 +10662,7 @@
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10641,10 +10674,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="G30">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -10662,7 +10695,7 @@
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10674,13 +10707,13 @@
         <v>0</v>
       </c>
       <c r="F31">
+        <v>20000</v>
+      </c>
+      <c r="G31">
         <v>10000</v>
       </c>
-      <c r="G31">
-        <v>5000</v>
-      </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -10695,7 +10728,7 @@
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10707,13 +10740,13 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G32">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -10728,7 +10761,7 @@
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10740,10 +10773,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>20000</v>
+        <v>500</v>
       </c>
       <c r="G33">
-        <v>10000</v>
+        <v>250</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -10761,7 +10794,7 @@
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -10773,13 +10806,13 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G34">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -10794,7 +10827,7 @@
         <v>30033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -10806,150 +10839,18 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="G35">
-        <v>250</v>
+        <v>1400</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <f t="shared" si="0"/>
-        <v>30034</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>700</v>
-      </c>
-      <c r="G36">
-        <v>350</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <f t="shared" si="0"/>
-        <v>30035</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>500</v>
-      </c>
-      <c r="G37">
-        <v>250</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <f t="shared" si="0"/>
-        <v>30036</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>3000</v>
-      </c>
-      <c r="G38">
-        <v>1500</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <f t="shared" si="0"/>
-        <v>30037</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>2800</v>
-      </c>
-      <c r="G39">
-        <v>1400</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD0F2DF-0299-4C2A-B4DA-D29D3E7C05C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049260DE-7BA9-4347-B273-C2268A872053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="195">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -811,6 +811,10 @@
   </si>
   <si>
     <t>donuts_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>blue_jemstone</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4650,7 +4654,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -4727,7 +4731,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A55" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A56" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5376,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -5409,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -5442,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -5622,25 +5626,25 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>6</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -5655,7 +5659,7 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -5664,13 +5668,13 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>2000</v>
@@ -5688,7 +5692,7 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -5721,7 +5725,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -5754,7 +5758,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -5772,7 +5776,7 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -5787,7 +5791,7 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -5805,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -5820,7 +5824,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -5838,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -5853,7 +5857,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -5871,7 +5875,7 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -5886,7 +5890,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -5904,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -5919,7 +5923,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -5937,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -5952,7 +5956,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -5970,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -5985,7 +5989,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -6003,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6018,7 +6022,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -6036,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6051,7 +6055,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6069,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6084,7 +6088,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6093,16 +6097,16 @@
         <v>6</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>2000</v>
+        <v>2107</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6117,7 +6121,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6150,7 +6154,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6162,13 +6166,13 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6183,7 +6187,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6195,13 +6199,13 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -6216,7 +6220,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6249,7 +6253,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6261,10 +6265,10 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H49">
         <v>2000</v>
@@ -6282,7 +6286,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6291,13 +6295,13 @@
         <v>6</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H50">
         <v>2000</v>
@@ -6315,7 +6319,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6348,7 +6352,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6360,10 +6364,10 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>2000</v>
@@ -6381,7 +6385,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6414,7 +6418,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6447,7 +6451,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6471,6 +6475,39 @@
         <v>0</v>
       </c>
       <c r="J55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>2054</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>2000</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049260DE-7BA9-4347-B273-C2268A872053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DBE51B-19E4-4EEB-B4CE-4E9168093279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -6238,7 +6238,7 @@
         <v>2</v>
       </c>
       <c r="H48">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6370,7 +6370,7 @@
         <v>2</v>
       </c>
       <c r="H52">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -10348,7 +10348,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G19">
         <v>500</v>
@@ -10381,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G20">
         <v>500</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DBE51B-19E4-4EEB-B4CE-4E9168093279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2979599-0065-46EA-8454-745FDAAD2981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="585" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -9787,7 +9787,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>15</v>
@@ -9886,7 +9886,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="G5">
         <v>35</v>
@@ -11495,7 +11495,7 @@
         <v>2500</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2979599-0065-46EA-8454-745FDAAD2981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9850C996-4959-4FE6-BE6D-5D2D33BDE4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="585" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2670" yWindow="1125" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="195">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -8816,7 +8816,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" ref="A7:A15" si="1">ROW()-2+20000</f>
+        <f t="shared" ref="A7:A16" si="1">ROW()-2+20000</f>
         <v>20005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9063,7 +9063,7 @@
         <v>20006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -9075,10 +9075,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -9096,22 +9096,22 @@
         <v>20007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="C9">
         <v>50</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -9129,22 +9129,22 @@
         <v>20008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C10">
         <v>50</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -9162,25 +9162,25 @@
         <v>20009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2300</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -9195,7 +9195,7 @@
         <v>20010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -9207,13 +9207,13 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1500</v>
+        <v>2300</v>
       </c>
       <c r="G12">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -9228,7 +9228,7 @@
         <v>20011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -9240,10 +9240,10 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>1500</v>
+      </c>
+      <c r="G13">
         <v>500</v>
-      </c>
-      <c r="G13">
-        <v>250</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -9261,7 +9261,7 @@
         <v>20012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -9294,19 +9294,19 @@
         <v>20013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G15">
         <v>250</v>
@@ -9323,26 +9323,26 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" ref="A16:A27" si="2">ROW()-2+20000</f>
+        <f t="shared" si="1"/>
         <v>20014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="G16">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -9356,11 +9356,11 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A17:A29" si="2">ROW()-2+20000</f>
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -9372,10 +9372,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G17">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -9393,7 +9393,7 @@
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -9405,10 +9405,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="G18">
-        <v>650</v>
+        <v>50</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -9426,7 +9426,7 @@
         <v>20017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -9438,10 +9438,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G19">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -9459,7 +9459,7 @@
         <v>20018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -9471,10 +9471,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>3000</v>
+        <v>1300</v>
       </c>
       <c r="G20">
-        <v>1500</v>
+        <v>650</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -9492,7 +9492,7 @@
         <v>20019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -9504,10 +9504,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G21">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -9525,7 +9525,7 @@
         <v>20020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -9537,10 +9537,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="G22">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -9558,7 +9558,7 @@
         <v>20021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -9570,10 +9570,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G23">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -9591,7 +9591,7 @@
         <v>20022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -9603,10 +9603,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G24">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -9624,7 +9624,7 @@
         <v>20023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -9636,10 +9636,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="G25">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -9657,7 +9657,7 @@
         <v>20024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -9669,13 +9669,13 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G26">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -9690,30 +9690,96 @@
         <v>20025</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>4000</v>
+      </c>
+      <c r="G27">
+        <v>2000</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f t="shared" si="2"/>
+        <v>20026</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>500</v>
+      </c>
+      <c r="G28">
+        <v>250</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <f t="shared" si="2"/>
+        <v>20027</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>3000</v>
       </c>
-      <c r="G27">
+      <c r="G29">
         <v>1500</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27">
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <v>1</v>
       </c>
     </row>
@@ -9726,7 +9792,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9771,7 +9837,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A35" si="0">ROW()-2+30000</f>
+        <f>ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9804,7 +9870,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -9837,7 +9903,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -9870,7 +9936,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30003</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -9903,7 +9969,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -9936,7 +10002,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -9969,7 +10035,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30006</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -10002,7 +10068,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -10035,7 +10101,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -10068,7 +10134,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -10101,7 +10167,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -10134,7 +10200,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10167,7 +10233,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -10200,7 +10266,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10233,7 +10299,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -10266,7 +10332,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -10299,7 +10365,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -10332,7 +10398,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -10365,7 +10431,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -10398,7 +10464,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -10431,7 +10497,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -10464,7 +10530,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -10497,7 +10563,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -10530,11 +10596,11 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -10546,10 +10612,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G25">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -10563,11 +10629,11 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -10579,10 +10645,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G26">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -10596,11 +10662,11 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -10612,10 +10678,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -10629,11 +10695,11 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -10645,13 +10711,13 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G28">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -10662,11 +10728,11 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10678,13 +10744,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G29">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -10695,11 +10761,11 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10711,10 +10777,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G30">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -10728,11 +10794,11 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10744,13 +10810,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>20000</v>
+        <v>500</v>
       </c>
       <c r="G31">
-        <v>10000</v>
+        <v>250</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -10761,11 +10827,11 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10783,7 +10849,7 @@
         <v>250</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -10794,11 +10860,11 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10810,10 +10876,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G33">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -10827,11 +10893,11 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
-        <f t="shared" si="0"/>
+        <f>ROW()-2+30000</f>
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -10843,51 +10909,18 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>700</v>
+        <v>2800</v>
       </c>
       <c r="G34">
-        <v>350</v>
+        <v>1400</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <f t="shared" si="0"/>
-        <v>30033</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>2800</v>
-      </c>
-      <c r="G35">
-        <v>1400</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9850C996-4959-4FE6-BE6D-5D2D33BDE4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F56C8E1-6C4A-4EB8-B7E8-D29065FEAAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="1125" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2505" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="197">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -815,6 +815,14 @@
   </si>
   <si>
     <t>blue_jemstone</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cakemold_stainless</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cake_rolltable</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6520,7 +6528,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DBDC14-7E25-4116-BA5C-8148F52CCF05}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -6565,7 +6573,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>ROW()-2+10000</f>
+        <f t="shared" ref="A2:A33" si="0">ROW()-2+10000</f>
         <v>10000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -6598,7 +6606,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f>ROW()-2+10000</f>
+        <f t="shared" si="0"/>
         <v>10001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -6631,7 +6639,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" ref="A4:A67" si="0">ROW()-2+10000</f>
+        <f t="shared" si="0"/>
         <v>10002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -7621,7 +7629,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A34:A66" si="1">ROW()-2+10000</f>
         <v>10032</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -7654,7 +7662,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10033</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -7687,7 +7695,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10034</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -7720,7 +7728,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10035</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -7753,7 +7761,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10036</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -7786,7 +7794,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10037</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -7819,11 +7827,11 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -7835,13 +7843,13 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="G40">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -7852,11 +7860,11 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>66</v>
+        <v>196</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -7868,13 +7876,13 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="G41">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -7885,11 +7893,11 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -7901,10 +7909,10 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="G42">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -7918,11 +7926,11 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -7934,10 +7942,10 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>20000</v>
+        <v>1500</v>
       </c>
       <c r="G43">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -7951,11 +7959,11 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -7967,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G44">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -7984,29 +7992,29 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="G45">
-        <v>250</v>
+        <v>10000</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -8017,26 +8025,26 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>1000</v>
+        <v>50000</v>
       </c>
       <c r="G46">
-        <v>500</v>
+        <v>25000</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -8050,11 +8058,11 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -8066,13 +8074,13 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G47">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -8083,11 +8091,11 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -8099,10 +8107,10 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="G48">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -8116,11 +8124,11 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -8132,13 +8140,13 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="G49">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -8149,11 +8157,11 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -8165,13 +8173,13 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="G50">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -8182,11 +8190,11 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -8198,13 +8206,13 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>3000</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -8215,11 +8223,11 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -8231,13 +8239,13 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="G52">
-        <v>2500</v>
+        <v>750</v>
       </c>
       <c r="H52">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -8248,11 +8256,11 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -8264,13 +8272,13 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>5000</v>
+        <v>10</v>
       </c>
       <c r="G53">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -8281,11 +8289,11 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -8297,13 +8305,13 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G54">
-        <v>3750</v>
+        <v>2500</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -8314,29 +8322,29 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="G55">
-        <v>50</v>
+        <v>2500</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>
@@ -8347,29 +8355,29 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>150</v>
+        <v>7500</v>
       </c>
       <c r="G56">
-        <v>75</v>
+        <v>3750</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -8380,11 +8388,11 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -8396,10 +8404,10 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G57">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -8413,11 +8421,11 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -8429,13 +8437,13 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G58">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -8446,11 +8454,11 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -8462,10 +8470,10 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="G59">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -8479,11 +8487,11 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -8495,13 +8503,13 @@
         <v>0</v>
       </c>
       <c r="F60">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="G60">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -8512,11 +8520,11 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -8545,11 +8553,11 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -8561,10 +8569,10 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="G62">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -8578,11 +8586,11 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -8594,10 +8602,10 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="G63">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -8611,11 +8619,11 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -8627,13 +8635,13 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G64">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -8644,11 +8652,11 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -8660,13 +8668,13 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G65">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -8677,11 +8685,11 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -8693,10 +8701,10 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G66">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -8710,11 +8718,11 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A67:A74" si="2">ROW()-2+10000</f>
         <v>10065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -8726,10 +8734,10 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G67">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -8743,11 +8751,11 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
-        <f t="shared" ref="A68:A69" si="1">ROW()-2+10000</f>
+        <f t="shared" si="2"/>
         <v>10066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>27</v>
+        <v>193</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -8759,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>10000</v>
+        <v>600</v>
       </c>
       <c r="G68">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -8776,34 +8784,199 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10067</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>10000</v>
+      </c>
+      <c r="G69">
+        <v>5000</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <f t="shared" si="2"/>
+        <v>10068</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>1000</v>
+      </c>
+      <c r="G70">
+        <v>500</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <f t="shared" si="2"/>
+        <v>10069</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>3000</v>
+      </c>
+      <c r="G71">
+        <v>1500</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <f t="shared" si="2"/>
+        <v>10070</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>500</v>
+      </c>
+      <c r="G72">
+        <v>250</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <f t="shared" si="2"/>
+        <v>10071</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>800</v>
+      </c>
+      <c r="G73">
+        <v>400</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <f t="shared" si="2"/>
+        <v>10072</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69">
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
         <v>700</v>
       </c>
-      <c r="G69">
+      <c r="G74">
         <v>350</v>
       </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69" t="b">
-        <v>0</v>
-      </c>
-      <c r="J69">
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74">
         <v>1</v>
       </c>
     </row>
@@ -8816,7 +8989,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9356,7 +9529,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" ref="A17:A29" si="2">ROW()-2+20000</f>
+        <f t="shared" ref="A17:A30" si="2">ROW()-2+20000</f>
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -9624,7 +9797,7 @@
         <v>20023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -9636,10 +9809,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G25">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -9657,7 +9830,7 @@
         <v>20024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -9669,13 +9842,13 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G26">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -9690,7 +9863,7 @@
         <v>20025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -9702,13 +9875,13 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="G27">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -9723,7 +9896,7 @@
         <v>20026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -9735,13 +9908,13 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="G28">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -9756,30 +9929,63 @@
         <v>20027</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>500</v>
+      </c>
+      <c r="G29">
+        <v>250</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <f t="shared" si="2"/>
+        <v>20028</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
         <v>3000</v>
       </c>
-      <c r="G29">
+      <c r="G30">
         <v>1500</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <v>1</v>
       </c>
     </row>
@@ -9792,7 +9998,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9837,7 +10043,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>ROW()-2+30000</f>
+        <f t="shared" ref="A2:A31" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -9870,7 +10076,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -9903,7 +10109,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30002</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -9936,7 +10142,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30003</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -9969,7 +10175,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30004</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -10002,7 +10208,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -10035,7 +10241,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30006</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -10068,7 +10274,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -10101,7 +10307,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -10134,7 +10340,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -10167,7 +10373,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -10200,7 +10406,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10233,7 +10439,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -10266,7 +10472,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10299,7 +10505,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -10332,7 +10538,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -10365,7 +10571,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -10398,11 +10604,11 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -10414,10 +10620,10 @@
         <v>0</v>
       </c>
       <c r="F19">
+        <v>10000</v>
+      </c>
+      <c r="G19">
         <v>5000</v>
-      </c>
-      <c r="G19">
-        <v>500</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -10431,7 +10637,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -10464,7 +10670,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -10497,7 +10703,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -10530,7 +10736,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -10563,7 +10769,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -10596,7 +10802,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -10629,7 +10835,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -10662,11 +10868,11 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -10678,10 +10884,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="G27">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -10695,11 +10901,11 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -10711,10 +10917,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="G28">
-        <v>5000</v>
+        <v>250</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -10728,11 +10934,11 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10744,10 +10950,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G29">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -10761,11 +10967,11 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10777,10 +10983,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>20000</v>
+        <v>700</v>
       </c>
       <c r="G30">
-        <v>10000</v>
+        <v>350</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -10794,11 +11000,11 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
-        <f>ROW()-2+30000</f>
+        <f t="shared" si="0"/>
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10810,10 +11016,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="G31">
-        <v>250</v>
+        <v>1400</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -10822,105 +11028,6 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <f>ROW()-2+30000</f>
-        <v>30030</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>500</v>
-      </c>
-      <c r="G32">
-        <v>250</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <f>ROW()-2+30000</f>
-        <v>30031</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>700</v>
-      </c>
-      <c r="G33">
-        <v>350</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <f>ROW()-2+30000</f>
-        <v>30032</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>2800</v>
-      </c>
-      <c r="G34">
-        <v>1400</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F56C8E1-6C4A-4EB8-B7E8-D29065FEAAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB32F616-6529-4F3A-9FAE-94D15CFBAEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="199">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -823,6 +823,14 @@
   </si>
   <si>
     <t>cake_rolltable</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_rare_findUP_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>area_num</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1193,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2154E2-30EB-484D-B7C9-48FD8223AE77}">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1201,10 +1209,11 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>155</v>
       </c>
@@ -1233,10 +1242,13 @@
         <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <f>ROW()-2</f>
         <v>0</v>
@@ -1268,8 +1280,11 @@
       <c r="J2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <f t="shared" ref="A3:A34" si="0">ROW()-2</f>
         <v>1</v>
@@ -1301,8 +1316,11 @@
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1334,8 +1352,11 @@
       <c r="J4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1367,8 +1388,11 @@
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1400,8 +1424,11 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1433,8 +1460,11 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1466,8 +1496,11 @@
       <c r="J8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1499,8 +1532,11 @@
       <c r="J9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1532,8 +1568,11 @@
       <c r="J10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1565,8 +1604,11 @@
       <c r="J11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1598,8 +1640,11 @@
       <c r="J12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1631,8 +1676,11 @@
       <c r="J13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1664,8 +1712,11 @@
       <c r="J14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1697,8 +1748,11 @@
       <c r="J15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1730,8 +1784,11 @@
       <c r="J16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1763,8 +1820,11 @@
       <c r="J17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1796,8 +1856,11 @@
       <c r="J18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1829,8 +1892,11 @@
       <c r="J19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1862,8 +1928,11 @@
       <c r="J20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1895,8 +1964,11 @@
       <c r="J21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1928,8 +2000,11 @@
       <c r="J22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1961,8 +2036,11 @@
       <c r="J23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1994,8 +2072,11 @@
       <c r="J24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2027,8 +2108,11 @@
       <c r="J25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2060,8 +2144,11 @@
       <c r="J26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2093,8 +2180,11 @@
       <c r="J27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2126,8 +2216,11 @@
       <c r="J28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2159,8 +2252,11 @@
       <c r="J29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2192,8 +2288,11 @@
       <c r="J30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2225,8 +2324,11 @@
       <c r="J31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2258,8 +2360,11 @@
       <c r="J32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2291,8 +2396,11 @@
       <c r="J33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2324,8 +2432,11 @@
       <c r="J34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" ref="A35:A67" si="1">ROW()-2</f>
         <v>33</v>
@@ -2357,8 +2468,11 @@
       <c r="J35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -2390,8 +2504,11 @@
       <c r="J36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -2423,8 +2540,11 @@
       <c r="J37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -2456,8 +2576,11 @@
       <c r="J38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -2489,8 +2612,11 @@
       <c r="J39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -2522,8 +2648,11 @@
       <c r="J40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -2555,8 +2684,11 @@
       <c r="J41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -2588,8 +2720,11 @@
       <c r="J42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -2621,8 +2756,11 @@
       <c r="J43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -2654,8 +2792,11 @@
       <c r="J44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -2687,8 +2828,11 @@
       <c r="J45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -2720,8 +2864,11 @@
       <c r="J46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -2753,8 +2900,11 @@
       <c r="J47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -2786,8 +2936,11 @@
       <c r="J48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -2819,8 +2972,11 @@
       <c r="J49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2852,8 +3008,11 @@
       <c r="J50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -2885,8 +3044,11 @@
       <c r="J51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2918,8 +3080,11 @@
       <c r="J52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -2951,8 +3116,11 @@
       <c r="J53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -2984,8 +3152,11 @@
       <c r="J54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -3017,8 +3188,11 @@
       <c r="J55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -3050,8 +3224,11 @@
       <c r="J56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -3083,8 +3260,11 @@
       <c r="J57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -3116,8 +3296,11 @@
       <c r="J58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -3149,8 +3332,11 @@
       <c r="J59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <f t="shared" si="1"/>
         <v>58</v>
@@ -3182,8 +3368,11 @@
       <c r="J60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <f t="shared" si="1"/>
         <v>59</v>
@@ -3215,8 +3404,11 @@
       <c r="J61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>60</v>
@@ -3248,8 +3440,11 @@
       <c r="J62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>61</v>
@@ -3281,8 +3476,11 @@
       <c r="J63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <f t="shared" si="1"/>
         <v>62</v>
@@ -3314,8 +3512,11 @@
       <c r="J64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -3347,8 +3548,11 @@
       <c r="J65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <f t="shared" si="1"/>
         <v>64</v>
@@ -3380,8 +3584,11 @@
       <c r="J66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <f t="shared" si="1"/>
         <v>65</v>
@@ -3413,8 +3620,11 @@
       <c r="J67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" ref="A68:A76" si="2">ROW()-2</f>
         <v>66</v>
@@ -3446,8 +3656,11 @@
       <c r="J68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3479,8 +3692,11 @@
       <c r="J69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3512,8 +3728,11 @@
       <c r="J70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3545,8 +3764,11 @@
       <c r="J71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3578,8 +3800,11 @@
       <c r="J72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3611,8 +3836,11 @@
       <c r="J73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3644,8 +3872,11 @@
       <c r="J74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3677,8 +3908,11 @@
       <c r="J75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3708,6 +3942,9 @@
         <v>0</v>
       </c>
       <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
         <v>1</v>
       </c>
     </row>
@@ -3720,7 +3957,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6706A2-EDB2-4593-B696-68963F977CA9}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -3730,7 +3967,7 @@
     <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>155</v>
       </c>
@@ -3759,10 +3996,13 @@
         <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <f>ROW()-2+1000</f>
         <v>1000</v>
@@ -3792,10 +4032,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <f t="shared" ref="A3:A28" si="0">ROW()-2+1000</f>
         <v>1001</v>
@@ -3825,10 +4068,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>1002</v>
@@ -3858,10 +4104,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>1003</v>
@@ -3891,10 +4140,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1004</v>
@@ -3924,10 +4176,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1005</v>
@@ -3957,10 +4212,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1006</v>
@@ -3990,10 +4248,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1007</v>
@@ -4023,10 +4284,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1008</v>
@@ -4056,10 +4320,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1009</v>
@@ -4089,10 +4356,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1010</v>
@@ -4122,10 +4392,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>1011</v>
@@ -4155,10 +4428,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>1012</v>
@@ -4188,10 +4464,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>1013</v>
@@ -4221,10 +4500,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>1014</v>
@@ -4254,10 +4536,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>1015</v>
@@ -4287,10 +4572,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>1016</v>
@@ -4320,10 +4608,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>1017</v>
@@ -4353,10 +4644,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>1018</v>
@@ -4386,10 +4680,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>1019</v>
@@ -4419,10 +4716,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>1020</v>
@@ -4452,10 +4752,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>1021</v>
@@ -4485,10 +4788,13 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>1022</v>
@@ -4518,10 +4824,13 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>1023</v>
@@ -4551,10 +4860,13 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>1024</v>
@@ -4584,10 +4896,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>1025</v>
@@ -4617,10 +4932,13 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>1026</v>
@@ -4650,6 +4968,9 @@
         <v>0</v>
       </c>
       <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28">
         <v>1</v>
       </c>
     </row>
@@ -4662,7 +4983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -4672,7 +4993,7 @@
     <col min="9" max="9" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>155</v>
       </c>
@@ -4701,10 +5022,13 @@
         <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <f>ROW()-2+2000</f>
         <v>2000</v>
@@ -4734,12 +5058,15 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A56" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A57" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4767,10 +5094,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2002</v>
@@ -4800,10 +5130,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>2003</v>
@@ -4833,10 +5166,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>2004</v>
@@ -4866,10 +5202,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>2005</v>
@@ -4899,10 +5238,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>2006</v>
@@ -4932,10 +5274,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>2007</v>
@@ -4965,10 +5310,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>2008</v>
@@ -4998,10 +5346,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>2009</v>
@@ -5031,10 +5382,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>2010</v>
@@ -5064,10 +5418,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>2011</v>
@@ -5097,10 +5454,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>2012</v>
@@ -5130,10 +5490,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>2013</v>
@@ -5163,10 +5526,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>2014</v>
@@ -5196,10 +5562,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>2015</v>
@@ -5229,10 +5598,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>2016</v>
@@ -5262,49 +5634,55 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>2017</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C19">
-        <v>50</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <f t="shared" si="0"/>
-        <v>2018</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C20">
         <v>50</v>
@@ -5328,16 +5706,19 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C21">
         <v>50</v>
@@ -5361,16 +5742,19 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>2020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22">
         <v>50</v>
@@ -5379,7 +5763,7 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -5388,22 +5772,25 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23">
         <v>50</v>
@@ -5427,16 +5814,19 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24">
         <v>50</v>
@@ -5460,16 +5850,19 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C25">
         <v>50</v>
@@ -5478,7 +5871,7 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -5487,55 +5880,61 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26">
+        <v>50</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <f t="shared" si="0"/>
-        <v>2025</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -5547,28 +5946,31 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -5580,28 +5982,31 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -5613,31 +6018,34 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -5646,10 +6054,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -5658,49 +6066,55 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>6</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -5709,13 +6123,13 @@
         <v>6</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>2000</v>
@@ -5724,16 +6138,19 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -5757,16 +6174,19 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -5790,16 +6210,19 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -5817,22 +6240,25 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -5850,22 +6276,25 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -5883,22 +6312,25 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -5916,22 +6348,25 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -5949,22 +6384,25 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -5982,22 +6420,25 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -6015,22 +6456,25 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -6048,22 +6492,25 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6081,22 +6528,25 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6114,22 +6564,25 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6138,31 +6591,34 @@
         <v>6</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>2000</v>
+        <v>2107</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6186,16 +6642,19 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6207,28 +6666,31 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6240,10 +6702,10 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -6252,16 +6714,19 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6279,22 +6744,25 @@
         <v>2</v>
       </c>
       <c r="H49">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6306,10 +6774,10 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H50">
         <v>2000</v>
@@ -6318,16 +6786,19 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6336,13 +6807,13 @@
         <v>6</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H51">
         <v>2000</v>
@@ -6351,16 +6822,19 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6378,22 +6852,25 @@
         <v>2</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6405,28 +6882,31 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6450,16 +6930,19 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6483,16 +6966,19 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -6516,6 +7002,45 @@
         <v>0</v>
       </c>
       <c r="J56">
+        <v>100</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>2055</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>3</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>2000</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>100</v>
+      </c>
+      <c r="K57">
         <v>1</v>
       </c>
     </row>
@@ -6528,7 +7053,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DBDC14-7E25-4116-BA5C-8148F52CCF05}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -6536,10 +7061,10 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>155</v>
       </c>
@@ -6568,10 +7093,13 @@
         <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <f t="shared" ref="A2:A33" si="0">ROW()-2+10000</f>
         <v>10000</v>
@@ -6601,10 +7129,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>10001</v>
@@ -6634,10 +7165,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>10002</v>
@@ -6667,10 +7201,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>10003</v>
@@ -6700,10 +7237,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>10004</v>
@@ -6733,10 +7273,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>10005</v>
@@ -6766,10 +7309,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>10006</v>
@@ -6799,10 +7345,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>10007</v>
@@ -6832,10 +7381,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>10008</v>
@@ -6865,10 +7417,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10009</v>
@@ -6898,10 +7453,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10010</v>
@@ -6931,10 +7489,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>10011</v>
@@ -6964,10 +7525,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>10012</v>
@@ -6997,10 +7561,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>10013</v>
@@ -7030,10 +7597,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>10014</v>
@@ -7063,10 +7633,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>10015</v>
@@ -7096,10 +7669,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>10016</v>
@@ -7129,10 +7705,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>10017</v>
@@ -7162,10 +7741,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>10018</v>
@@ -7195,10 +7777,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>10019</v>
@@ -7228,10 +7813,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>10020</v>
@@ -7261,10 +7849,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>10021</v>
@@ -7294,10 +7885,13 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10022</v>
@@ -7327,10 +7921,13 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>10023</v>
@@ -7360,10 +7957,13 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>10024</v>
@@ -7393,10 +7993,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>10025</v>
@@ -7426,10 +8029,13 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>10026</v>
@@ -7459,10 +8065,13 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>10027</v>
@@ -7492,10 +8101,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>10028</v>
@@ -7525,10 +8137,13 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>10029</v>
@@ -7558,10 +8173,13 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>10030</v>
@@ -7591,10 +8209,13 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>10031</v>
@@ -7624,10 +8245,13 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" ref="A34:A66" si="1">ROW()-2+10000</f>
         <v>10032</v>
@@ -7657,10 +8281,13 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>10033</v>
@@ -7690,10 +8317,13 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>10034</v>
@@ -7723,10 +8353,13 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>10035</v>
@@ -7756,10 +8389,13 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>10036</v>
@@ -7789,10 +8425,13 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>10037</v>
@@ -7822,10 +8461,13 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>10038</v>
@@ -7855,10 +8497,13 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>10039</v>
@@ -7888,10 +8533,13 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>10040</v>
@@ -7921,10 +8569,13 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>10041</v>
@@ -7954,10 +8605,13 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>10042</v>
@@ -7987,10 +8641,13 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>10043</v>
@@ -8020,10 +8677,13 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>10044</v>
@@ -8053,10 +8713,13 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>10045</v>
@@ -8086,10 +8749,13 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>10046</v>
@@ -8119,10 +8785,13 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>10047</v>
@@ -8152,10 +8821,13 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>10048</v>
@@ -8185,10 +8857,13 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>10049</v>
@@ -8218,10 +8893,13 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>10050</v>
@@ -8251,10 +8929,13 @@
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>10051</v>
@@ -8284,10 +8965,13 @@
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>10052</v>
@@ -8317,10 +9001,13 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>10053</v>
@@ -8350,10 +9037,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>10054</v>
@@ -8383,10 +9073,13 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>10055</v>
@@ -8416,10 +9109,13 @@
         <v>0</v>
       </c>
       <c r="J57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>10056</v>
@@ -8449,10 +9145,13 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>10057</v>
@@ -8482,10 +9181,13 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <f t="shared" si="1"/>
         <v>10058</v>
@@ -8515,10 +9217,13 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <f t="shared" si="1"/>
         <v>10059</v>
@@ -8548,10 +9253,13 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>10060</v>
@@ -8581,10 +9289,13 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>10061</v>
@@ -8614,10 +9325,13 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <f t="shared" si="1"/>
         <v>10062</v>
@@ -8647,10 +9361,13 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>10063</v>
@@ -8680,10 +9397,13 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <f t="shared" si="1"/>
         <v>10064</v>
@@ -8713,10 +9433,13 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <f t="shared" ref="A67:A74" si="2">ROW()-2+10000</f>
         <v>10065</v>
@@ -8746,10 +9469,13 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" si="2"/>
         <v>10066</v>
@@ -8779,10 +9505,13 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="2"/>
         <v>10067</v>
@@ -8812,10 +9541,13 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="2"/>
         <v>10068</v>
@@ -8845,10 +9577,13 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <f t="shared" si="2"/>
         <v>10069</v>
@@ -8878,10 +9613,13 @@
         <v>0</v>
       </c>
       <c r="J71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="2"/>
         <v>10070</v>
@@ -8911,10 +9649,13 @@
         <v>0</v>
       </c>
       <c r="J72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="2"/>
         <v>10071</v>
@@ -8944,10 +9685,13 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="2"/>
         <v>10072</v>
@@ -8977,6 +9721,9 @@
         <v>0</v>
       </c>
       <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
         <v>1</v>
       </c>
     </row>
@@ -8989,7 +9736,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -8997,10 +9744,10 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>155</v>
       </c>
@@ -9029,10 +9776,13 @@
         <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <f t="shared" ref="A2:A6" si="0">ROW()-2+20000</f>
         <v>20000</v>
@@ -9062,10 +9812,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>20001</v>
@@ -9095,10 +9848,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>20002</v>
@@ -9128,10 +9884,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>20003</v>
@@ -9161,10 +9920,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>20004</v>
@@ -9194,10 +9956,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" ref="A7:A16" si="1">ROW()-2+20000</f>
         <v>20005</v>
@@ -9227,10 +9992,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="1"/>
         <v>20006</v>
@@ -9260,10 +10028,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="1"/>
         <v>20007</v>
@@ -9293,10 +10064,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>20008</v>
@@ -9326,10 +10100,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>20009</v>
@@ -9359,10 +10136,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>20010</v>
@@ -9392,10 +10172,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>20011</v>
@@ -9425,10 +10208,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>20012</v>
@@ -9458,10 +10244,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>20013</v>
@@ -9491,10 +10280,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>20014</v>
@@ -9524,10 +10316,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" ref="A17:A30" si="2">ROW()-2+20000</f>
         <v>20015</v>
@@ -9557,10 +10352,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="2"/>
         <v>20016</v>
@@ -9590,10 +10388,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="2"/>
         <v>20017</v>
@@ -9623,10 +10424,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="2"/>
         <v>20018</v>
@@ -9656,10 +10460,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="2"/>
         <v>20019</v>
@@ -9689,10 +10496,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="2"/>
         <v>20020</v>
@@ -9722,10 +10532,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="2"/>
         <v>20021</v>
@@ -9755,10 +10568,13 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="2"/>
         <v>20022</v>
@@ -9788,10 +10604,13 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="2"/>
         <v>20023</v>
@@ -9821,10 +10640,13 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="2"/>
         <v>20024</v>
@@ -9854,10 +10676,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="2"/>
         <v>20025</v>
@@ -9887,10 +10712,13 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="2"/>
         <v>20026</v>
@@ -9920,10 +10748,13 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="2"/>
         <v>20027</v>
@@ -9953,10 +10784,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1010</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="2"/>
         <v>20028</v>
@@ -9986,6 +10820,9 @@
         <v>0</v>
       </c>
       <c r="J30">
+        <v>1010</v>
+      </c>
+      <c r="K30">
         <v>1</v>
       </c>
     </row>
@@ -9998,7 +10835,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -10006,10 +10843,10 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>155</v>
       </c>
@@ -10038,10 +10875,13 @@
         <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <f t="shared" ref="A2:A31" si="0">ROW()-2+30000</f>
         <v>30000</v>
@@ -10071,10 +10911,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>30001</v>
@@ -10104,10 +10947,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>30002</v>
@@ -10137,10 +10983,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>30003</v>
@@ -10170,10 +11019,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>30004</v>
@@ -10203,10 +11055,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>30005</v>
@@ -10236,10 +11091,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>30006</v>
@@ -10269,10 +11127,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>30007</v>
@@ -10302,10 +11163,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>30008</v>
@@ -10335,10 +11199,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>30009</v>
@@ -10368,10 +11235,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>30010</v>
@@ -10401,10 +11271,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>30011</v>
@@ -10434,10 +11307,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>30012</v>
@@ -10467,10 +11343,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>30013</v>
@@ -10500,10 +11379,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>30014</v>
@@ -10533,10 +11415,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>30015</v>
@@ -10566,10 +11451,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>30016</v>
@@ -10599,10 +11487,13 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>30017</v>
@@ -10632,10 +11523,13 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>30018</v>
@@ -10665,10 +11559,13 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>30019</v>
@@ -10698,10 +11595,13 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>30020</v>
@@ -10731,10 +11631,13 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>30021</v>
@@ -10764,10 +11667,13 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>30022</v>
@@ -10797,10 +11703,13 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>30023</v>
@@ -10830,10 +11739,13 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>30024</v>
@@ -10863,10 +11775,13 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>30025</v>
@@ -10896,10 +11811,13 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>30026</v>
@@ -10929,10 +11847,13 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>30027</v>
@@ -10962,10 +11883,13 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>30028</v>
@@ -10995,10 +11919,13 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1020</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30029</v>
@@ -11028,6 +11955,9 @@
         <v>0</v>
       </c>
       <c r="J31">
+        <v>1020</v>
+      </c>
+      <c r="K31">
         <v>1</v>
       </c>
     </row>
@@ -11040,7 +11970,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4060CA39-02FB-4508-8603-5A906A5C9777}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11048,10 +11978,10 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="12.85546875" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>155</v>
       </c>
@@ -11080,10 +12010,13 @@
         <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <f t="shared" ref="A2:A17" si="0">ROW()-2+40000</f>
         <v>40000</v>
@@ -11113,10 +12046,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>40001</v>
@@ -11146,10 +12082,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>40002</v>
@@ -11179,10 +12118,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>40003</v>
@@ -11212,10 +12154,13 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>40004</v>
@@ -11245,10 +12190,13 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>40005</v>
@@ -11278,10 +12226,13 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>40006</v>
@@ -11311,10 +12262,13 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>40007</v>
@@ -11344,10 +12298,13 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>40008</v>
@@ -11377,10 +12334,13 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>40009</v>
@@ -11410,10 +12370,13 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>40010</v>
@@ -11443,10 +12406,13 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>40011</v>
@@ -11476,10 +12442,13 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>40012</v>
@@ -11509,10 +12478,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>40013</v>
@@ -11542,10 +12514,13 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>40014</v>
@@ -11575,10 +12550,13 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>40015</v>
@@ -11608,10 +12586,13 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1030</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" ref="A18" si="1">ROW()-2+40000</f>
         <v>40016</v>
@@ -11641,6 +12622,9 @@
         <v>0</v>
       </c>
       <c r="J18">
+        <v>1030</v>
+      </c>
+      <c r="K18">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB32F616-6529-4F3A-9FAE-94D15CFBAEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F362F8-8A23-49E3-8EE5-C982F11291C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="200">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -831,6 +831,10 @@
   </si>
   <si>
     <t>area_num</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cola_recipi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4983,7 +4987,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5066,7 +5070,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A57" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A58" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5646,7 +5650,7 @@
         <v>2017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -5658,10 +5662,10 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -5682,25 +5686,25 @@
         <v>2018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -5718,7 +5722,7 @@
         <v>2019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21">
         <v>50</v>
@@ -5754,7 +5758,7 @@
         <v>2020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C22">
         <v>50</v>
@@ -5790,7 +5794,7 @@
         <v>2021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C23">
         <v>50</v>
@@ -5799,7 +5803,7 @@
         <v>3</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -5808,7 +5812,7 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -5826,7 +5830,7 @@
         <v>2022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C24">
         <v>50</v>
@@ -5862,7 +5866,7 @@
         <v>2023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25">
         <v>50</v>
@@ -5898,7 +5902,7 @@
         <v>2024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C26">
         <v>50</v>
@@ -5907,7 +5911,7 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -5916,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -5934,25 +5938,25 @@
         <v>2025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -5970,7 +5974,7 @@
         <v>2026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -5982,13 +5986,13 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -6006,7 +6010,7 @@
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6018,13 +6022,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -6042,7 +6046,7 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -6054,13 +6058,13 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -6078,10 +6082,10 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -6090,10 +6094,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -6114,25 +6118,25 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>6</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -6150,7 +6154,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6159,13 +6163,13 @@
         <v>6</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>2000</v>
@@ -6186,7 +6190,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6222,7 +6226,7 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6258,7 +6262,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6276,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -6294,7 +6298,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6312,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6330,7 +6334,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6348,7 +6352,7 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -6366,7 +6370,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -6384,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6402,7 +6406,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -6420,7 +6424,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6438,7 +6442,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -6456,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6474,7 +6478,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -6492,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6510,7 +6514,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6528,7 +6532,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6546,7 +6550,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6564,7 +6568,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6582,7 +6586,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6600,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6618,7 +6622,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6627,16 +6631,16 @@
         <v>6</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>2000</v>
+        <v>2107</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6654,7 +6658,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6690,7 +6694,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6702,13 +6706,13 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6726,7 +6730,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6738,10 +6742,10 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -6762,7 +6766,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6780,7 +6784,7 @@
         <v>2</v>
       </c>
       <c r="H50">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6798,7 +6802,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6810,10 +6814,10 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H51">
         <v>2000</v>
@@ -6834,7 +6838,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6843,13 +6847,13 @@
         <v>6</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H52">
         <v>2000</v>
@@ -6870,7 +6874,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6888,7 +6892,7 @@
         <v>2</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -6906,7 +6910,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6918,13 +6922,13 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -6942,7 +6946,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6978,7 +6982,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7014,7 +7018,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7041,6 +7045,42 @@
         <v>100</v>
       </c>
       <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>2056</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>2000</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>100</v>
+      </c>
+      <c r="K58">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F362F8-8A23-49E3-8EE5-C982F11291C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C2F05F-9CCE-4DE4-8220-E55257460CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1755" yWindow="1035" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="203">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -835,6 +835,18 @@
   </si>
   <si>
     <t>cola_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_parfe_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_arrange1_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chocolate_arrange2_recipi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4987,7 +4999,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5070,7 +5082,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A58" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A61" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5686,7 +5698,7 @@
         <v>2018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -5698,13 +5710,13 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -5722,13 +5734,13 @@
         <v>2019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5758,22 +5770,22 @@
         <v>2020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>113</v>
+        <v>202</v>
       </c>
       <c r="C22">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>3</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
+      <c r="G22">
         <v>2</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -5794,25 +5806,25 @@
         <v>2021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -5830,7 +5842,7 @@
         <v>2022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C24">
         <v>50</v>
@@ -5839,7 +5851,7 @@
         <v>3</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -5848,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -5866,7 +5878,7 @@
         <v>2023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C25">
         <v>50</v>
@@ -5875,7 +5887,7 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -5884,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -5902,7 +5914,7 @@
         <v>2024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C26">
         <v>50</v>
@@ -5911,7 +5923,7 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -5920,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -5938,7 +5950,7 @@
         <v>2025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C27">
         <v>50</v>
@@ -5947,7 +5959,7 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -5956,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -5974,19 +5986,19 @@
         <v>2026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -6010,25 +6022,25 @@
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -6046,25 +6058,25 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -6082,7 +6094,7 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6094,13 +6106,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -6118,10 +6130,10 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>194</v>
+        <v>52</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -6130,10 +6142,10 @@
         <v>0</v>
       </c>
       <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
         <v>2</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -6154,7 +6166,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6163,16 +6175,16 @@
         <v>6</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>2</v>
       </c>
       <c r="H33">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -6190,7 +6202,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6202,13 +6214,13 @@
         <v>0</v>
       </c>
       <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34">
         <v>3</v>
       </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
       <c r="H34">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6226,10 +6238,10 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -6238,13 +6250,13 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6262,7 +6274,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6271,13 +6283,13 @@
         <v>6</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <v>2000</v>
@@ -6298,7 +6310,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6316,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6334,7 +6346,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6370,7 +6382,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -6388,7 +6400,7 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6406,7 +6418,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -6424,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6442,7 +6454,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -6460,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>2102</v>
+        <v>2000</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6478,7 +6490,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -6496,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6514,7 +6526,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6532,7 +6544,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6550,7 +6562,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6568,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6586,7 +6598,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6604,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6622,7 +6634,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6640,7 +6652,7 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>2107</v>
+        <v>2104</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6658,7 +6670,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6667,16 +6679,16 @@
         <v>6</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>2000</v>
+        <v>2105</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -6694,7 +6706,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6703,16 +6715,16 @@
         <v>6</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>2000</v>
+        <v>2106</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6730,7 +6742,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6739,16 +6751,16 @@
         <v>6</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>2107</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -6766,7 +6778,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6778,13 +6790,13 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G50">
         <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6802,7 +6814,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6814,7 +6826,7 @@
         <v>1</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -6838,7 +6850,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6850,13 +6862,13 @@
         <v>1</v>
       </c>
       <c r="F52">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -6874,7 +6886,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6883,16 +6895,16 @@
         <v>6</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G53">
         <v>2</v>
       </c>
       <c r="H53">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -6910,7 +6922,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6919,16 +6931,16 @@
         <v>6</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -6946,7 +6958,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6955,13 +6967,13 @@
         <v>6</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H55">
         <v>2000</v>
@@ -6982,7 +6994,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -6994,10 +7006,10 @@
         <v>0</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56">
         <v>2000</v>
@@ -7018,7 +7030,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7030,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -7054,7 +7066,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7081,6 +7093,114 @@
         <v>100</v>
       </c>
       <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>2057</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>2000</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>100</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>2058</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>6</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>2000</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>100</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>2059</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>6</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>2000</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>100</v>
+      </c>
+      <c r="K61">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C2F05F-9CCE-4DE4-8220-E55257460CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C46892-716C-4E2C-A6AF-1597F5B1E29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1035" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2775" yWindow="900" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="203">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -4999,7 +4999,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5082,7 +5082,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A61" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A62" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5698,7 +5698,7 @@
         <v>2018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -5710,10 +5710,10 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -5734,7 +5734,7 @@
         <v>2019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -5743,13 +5743,13 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
         <v>2</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -5770,7 +5770,7 @@
         <v>2020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -5782,10 +5782,10 @@
         <v>0</v>
       </c>
       <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22">
         <v>3</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -5818,13 +5818,13 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -6130,7 +6130,7 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6142,13 +6142,13 @@
         <v>0</v>
       </c>
       <c r="F32">
+        <v>10</v>
+      </c>
+      <c r="G32">
         <v>5</v>
       </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6178,13 +6178,13 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>2</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6214,13 +6214,13 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6238,10 +6238,10 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -6250,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -6274,25 +6274,25 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D36">
         <v>6</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -6310,7 +6310,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6319,13 +6319,13 @@
         <v>6</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37">
         <v>2000</v>
@@ -6346,7 +6346,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6382,7 +6382,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -6418,7 +6418,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -6436,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -6508,7 +6508,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6526,7 +6526,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6544,7 +6544,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6562,7 +6562,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6580,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6598,7 +6598,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6616,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6634,7 +6634,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6652,7 +6652,7 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6688,7 +6688,7 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -6706,7 +6706,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6724,7 +6724,7 @@
         <v>1</v>
       </c>
       <c r="H48">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6742,7 +6742,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6760,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6787,16 +6787,16 @@
         <v>6</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>2000</v>
+        <v>2107</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6814,7 +6814,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6850,7 +6850,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6862,13 +6862,13 @@
         <v>1</v>
       </c>
       <c r="F52">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -6886,7 +6886,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6898,10 +6898,10 @@
         <v>1</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -6922,7 +6922,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6940,7 +6940,7 @@
         <v>2</v>
       </c>
       <c r="H54">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -6958,7 +6958,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6970,10 +6970,10 @@
         <v>1</v>
       </c>
       <c r="F55">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>2000</v>
@@ -6994,7 +6994,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7003,13 +7003,13 @@
         <v>6</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H56">
         <v>2000</v>
@@ -7030,7 +7030,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7048,7 +7048,7 @@
         <v>2</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -7066,7 +7066,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7078,13 +7078,13 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -7102,7 +7102,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7138,7 +7138,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7174,7 +7174,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7201,6 +7201,42 @@
         <v>100</v>
       </c>
       <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>2060</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>6</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>2000</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>100</v>
+      </c>
+      <c r="K62">
         <v>1</v>
       </c>
     </row>
@@ -8651,7 +8687,7 @@
         <v>500</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -8687,7 +8723,7 @@
         <v>300</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -8795,7 +8831,7 @@
         <v>1500</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -8831,7 +8867,7 @@
         <v>10000</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -10320,10 +10356,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="G12">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -10896,10 +10932,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="G28">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -11497,7 +11533,7 @@
         <v>1500</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -11599,10 +11635,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="G17">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -11635,10 +11671,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="G18">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -11671,10 +11707,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="G19">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -11707,10 +11743,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="G20">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -11743,10 +11779,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="G21">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -11959,10 +11995,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G27">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -12266,10 +12302,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25000</v>
+        <v>4000</v>
       </c>
       <c r="G4">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -12374,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G7">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -12446,10 +12482,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>8000</v>
+        <v>3500</v>
       </c>
       <c r="G9">
-        <v>4000</v>
+        <v>1750</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -12482,10 +12518,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="G10">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -12662,10 +12698,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="G15">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -12734,10 +12770,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H17">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C46892-716C-4E2C-A6AF-1597F5B1E29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703526BA-76FF-4DFE-A0A7-11CD57219D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="900" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2715" yWindow="1095" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="204">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -847,6 +847,10 @@
   </si>
   <si>
     <t>chocolate_arrange2_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>siboribukuro_chocolate</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11031,7 +11035,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11079,7 +11083,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A31" si="0">ROW()-2+30000</f>
+        <f t="shared" ref="A2:A32" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -11803,25 +11807,25 @@
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>70</v>
+        <v>203</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="G22">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -11839,7 +11843,7 @@
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -11851,10 +11855,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -11875,7 +11879,7 @@
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -11887,13 +11891,13 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G24">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -11911,7 +11915,7 @@
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -11923,10 +11927,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G25">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -11947,7 +11951,7 @@
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -11959,10 +11963,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -11983,7 +11987,7 @@
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -11995,10 +11999,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="G27">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -12019,7 +12023,7 @@
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -12031,13 +12035,13 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="G28">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -12055,7 +12059,7 @@
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -12073,7 +12077,7 @@
         <v>250</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -12091,7 +12095,7 @@
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -12103,10 +12107,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G30">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -12127,7 +12131,7 @@
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -12139,13 +12143,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>2800</v>
+        <v>700</v>
       </c>
       <c r="G31">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -12154,6 +12158,42 @@
         <v>1020</v>
       </c>
       <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>30030</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>2800</v>
+      </c>
+      <c r="G32">
+        <v>1400</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1020</v>
+      </c>
+      <c r="K32">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703526BA-76FF-4DFE-A0A7-11CD57219D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F3E249-5ABB-4C84-8C8B-B135D349FBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="1095" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3135" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -4067,7 +4067,7 @@
         <v>104</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F3E249-5ABB-4C84-8C8B-B135D349FBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66665FDE-BE52-42AB-AA05-C26A323BFF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="975" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="205">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -851,6 +851,10 @@
   </si>
   <si>
     <t>siboribukuro_chocolate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_freezespell_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9936,7 +9940,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -10524,7 +10528,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" ref="A17:A30" si="2">ROW()-2+20000</f>
+        <f t="shared" ref="A17:A31" si="2">ROW()-2+20000</f>
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -10936,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="G28">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -10960,7 +10964,7 @@
         <v>20027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -10972,13 +10976,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="G29">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -10996,7 +11000,7 @@
         <v>20028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -11008,10 +11012,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G30">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -11023,6 +11027,42 @@
         <v>1010</v>
       </c>
       <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <f t="shared" si="2"/>
+        <v>20029</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>3000</v>
+      </c>
+      <c r="G31">
+        <v>1500</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1010</v>
+      </c>
+      <c r="K31">
         <v>1</v>
       </c>
     </row>
@@ -12342,10 +12382,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="G4">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -12522,10 +12562,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>3500</v>
+        <v>15000</v>
       </c>
       <c r="G9">
-        <v>1750</v>
+        <v>7500</v>
       </c>
       <c r="H9">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66665FDE-BE52-42AB-AA05-C26A323BFF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037F4422-E489-486C-B409-9F862F1DAA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="975" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="207">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -855,6 +855,14 @@
   </si>
   <si>
     <t>mg_freezespell_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gold_leaf</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cacao_mass</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9667,7 +9675,7 @@
         <v>150</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -10904,10 +10912,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G27">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -10982,7 +10990,7 @@
         <v>600</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -11075,7 +11083,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11123,7 +11131,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A32" si="0">ROW()-2+30000</f>
+        <f t="shared" ref="A2:A34" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -11379,7 +11387,7 @@
         <v>30007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="C9">
         <v>50</v>
@@ -11391,10 +11399,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -11415,7 +11423,7 @@
         <v>30008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -11427,10 +11435,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="G10">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -11451,22 +11459,22 @@
         <v>30009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>151</v>
+        <v>83</v>
       </c>
       <c r="C11">
         <v>50</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="G11">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -11487,7 +11495,7 @@
         <v>30010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -11502,7 +11510,7 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -11523,7 +11531,7 @@
         <v>30011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -11535,10 +11543,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -11559,25 +11567,25 @@
         <v>30012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>3000</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>1500</v>
+        <v>50</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -11595,25 +11603,25 @@
         <v>30013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>15000</v>
+        <v>200</v>
       </c>
       <c r="G15">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -11631,7 +11639,7 @@
         <v>30014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -11643,13 +11651,13 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="G16">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -11667,7 +11675,7 @@
         <v>30015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -11679,13 +11687,13 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="G17">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -11703,7 +11711,7 @@
         <v>30016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -11715,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="G18">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -11739,7 +11747,7 @@
         <v>30017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -11751,10 +11759,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -11775,7 +11783,7 @@
         <v>30018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -11787,10 +11795,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="G20">
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -11811,7 +11819,7 @@
         <v>30019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -11823,10 +11831,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="G21">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -11847,7 +11855,7 @@
         <v>30020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -11859,10 +11867,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="G22">
-        <v>250</v>
+        <v>1750</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -11883,25 +11891,25 @@
         <v>30021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="G23">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -11919,25 +11927,25 @@
         <v>30022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>203</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -11955,7 +11963,7 @@
         <v>30023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -11967,13 +11975,13 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G25">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -11991,7 +11999,7 @@
         <v>30024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -12003,13 +12011,13 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G26">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -12027,7 +12035,7 @@
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -12039,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -12063,7 +12071,7 @@
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -12075,10 +12083,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="G28">
-        <v>5000</v>
+        <v>150</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -12099,7 +12107,7 @@
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -12111,13 +12119,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="G29">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -12135,7 +12143,7 @@
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -12147,10 +12155,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="G30">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -12171,7 +12179,7 @@
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -12183,13 +12191,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G31">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -12207,7 +12215,7 @@
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>183</v>
+        <v>95</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -12219,13 +12227,13 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="G32">
-        <v>1400</v>
+        <v>250</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -12234,6 +12242,78 @@
         <v>1020</v>
       </c>
       <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>30031</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>700</v>
+      </c>
+      <c r="G33">
+        <v>350</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1020</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>30032</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>2800</v>
+      </c>
+      <c r="G34">
+        <v>1400</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1020</v>
+      </c>
+      <c r="K34">
         <v>1</v>
       </c>
     </row>
@@ -12784,7 +12864,7 @@
         <v>400</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -12820,7 +12900,7 @@
         <v>400</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037F4422-E489-486C-B409-9F862F1DAA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A780A2FE-2EA4-44F8-8871-EBFA5E31BD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="870" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -4148,7 +4148,7 @@
         <v>1003</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -4184,7 +4184,7 @@
         <v>1004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -4196,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -4220,7 +4220,7 @@
         <v>1005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C7">
         <v>50</v>
@@ -4232,13 +4232,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -4256,7 +4256,7 @@
         <v>1006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -4292,7 +4292,7 @@
         <v>1007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>50</v>
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -4328,7 +4328,7 @@
         <v>1008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -4340,10 +4340,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="G10">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -4364,7 +4364,7 @@
         <v>1009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="C11">
         <v>50</v>
@@ -4376,10 +4376,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="G11">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -4400,7 +4400,7 @@
         <v>1010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -4412,10 +4412,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -4436,7 +4436,7 @@
         <v>1011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -4448,10 +4448,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G13">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -4472,7 +4472,7 @@
         <v>1012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -4484,10 +4484,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -4508,7 +4508,7 @@
         <v>1013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="C15">
         <v>50</v>
@@ -4520,10 +4520,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H15">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A780A2FE-2EA4-44F8-8871-EBFA5E31BD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D235C3-0FA3-4D4B-8164-9F825ED27C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="870" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -7064,7 +7064,7 @@
         <v>2</v>
       </c>
       <c r="H57">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D235C3-0FA3-4D4B-8164-9F825ED27C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B075FF-83A6-4F2F-BA65-37E4B6B054BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="208">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -863,6 +863,10 @@
   </si>
   <si>
     <t>cacao_mass</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fantasian_cake_recipi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -12326,7 +12330,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4060CA39-02FB-4508-8603-5A906A5C9777}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -12374,7 +12378,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A17" si="0">ROW()-2+40000</f>
+        <f t="shared" ref="A2:A18" si="0">ROW()-2+40000</f>
         <v>40000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -12918,7 +12922,7 @@
         <v>40015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -12930,10 +12934,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="G17">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -12950,11 +12954,11 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" ref="A18" si="1">ROW()-2+40000</f>
+        <f t="shared" si="0"/>
         <v>40016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -12966,13 +12970,13 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="G18">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -12981,6 +12985,42 @@
         <v>1030</v>
       </c>
       <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f t="shared" ref="A19" si="1">ROW()-2+40000</f>
+        <v>40017</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>5000</v>
+      </c>
+      <c r="G19">
+        <v>2500</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1030</v>
+      </c>
+      <c r="K19">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B075FF-83A6-4F2F-BA65-37E4B6B054BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5B8391-2CDA-459F-A15A-BAA05D03FF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="960" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="213">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -867,6 +867,26 @@
   </si>
   <si>
     <t>fantasian_cake_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LavenderDress_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PinkUsagi_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Patissier_Costume</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DongriPochet_Acce</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PatissierHat_Acce</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5019,7 +5039,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5102,7 +5122,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A62" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A67" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5214,7 +5234,7 @@
         <v>2004</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -5223,10 +5243,10 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -5250,7 +5270,7 @@
         <v>2005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -5259,16 +5279,16 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -5286,7 +5306,7 @@
         <v>2006</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -5295,10 +5315,10 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -5322,7 +5342,7 @@
         <v>2007</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -5334,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -5358,7 +5378,7 @@
         <v>2008</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -5370,13 +5390,13 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -5394,7 +5414,7 @@
         <v>2009</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -5430,7 +5450,7 @@
         <v>2010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -5466,13 +5486,13 @@
         <v>2011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5484,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -5502,25 +5522,25 @@
         <v>2012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -5538,13 +5558,13 @@
         <v>2013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5553,10 +5573,10 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -5574,22 +5594,22 @@
         <v>2014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -5610,22 +5630,22 @@
         <v>2015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>120</v>
+        <v>212</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -5646,25 +5666,25 @@
         <v>2016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -5682,25 +5702,25 @@
         <v>2017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>199</v>
+        <v>123</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -5718,7 +5738,7 @@
         <v>2018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -5727,16 +5747,16 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
         <v>2</v>
       </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -5754,7 +5774,7 @@
         <v>2019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>202</v>
+        <v>110</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -5763,10 +5783,10 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -5790,7 +5810,7 @@
         <v>2020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -5799,13 +5819,13 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -5826,7 +5846,7 @@
         <v>2021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>197</v>
+        <v>121</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -5838,10 +5858,10 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -5862,22 +5882,22 @@
         <v>2022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="C24">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -5898,16 +5918,16 @@
         <v>2023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="C25">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -5934,22 +5954,22 @@
         <v>2024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="C26">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
         <v>3</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
+      <c r="G26">
         <v>2</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -5970,25 +5990,25 @@
         <v>2025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="C27">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27">
         <v>3</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -6006,25 +6026,25 @@
         <v>2026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
       <c r="C28">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
         <v>3</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
+      <c r="G28">
         <v>2</v>
       </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -6042,7 +6062,7 @@
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C29">
         <v>50</v>
@@ -6051,7 +6071,7 @@
         <v>3</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -6060,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -6078,7 +6098,7 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C30">
         <v>50</v>
@@ -6114,25 +6134,25 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -6150,22 +6170,22 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -6186,25 +6206,25 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -6222,22 +6242,22 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -6258,22 +6278,22 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -6294,10 +6314,10 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>6</v>
@@ -6306,13 +6326,13 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -6330,7 +6350,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6339,16 +6359,16 @@
         <v>6</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
         <v>5</v>
       </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
       <c r="H37">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6366,7 +6386,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6378,13 +6398,13 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -6402,7 +6422,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -6417,10 +6437,10 @@
         <v>3</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6438,7 +6458,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -6450,13 +6470,13 @@
         <v>0</v>
       </c>
       <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40">
         <v>3</v>
       </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
       <c r="H40">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6474,10 +6494,10 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>128</v>
+        <v>194</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -6486,13 +6506,13 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6510,7 +6530,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -6519,13 +6539,13 @@
         <v>6</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42">
         <v>2000</v>
@@ -6546,7 +6566,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6564,7 +6584,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6582,7 +6602,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6600,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2101</v>
+        <v>2000</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6618,7 +6638,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6636,7 +6656,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>2102</v>
+        <v>2000</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6654,7 +6674,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6672,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>2103</v>
+        <v>0</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6690,7 +6710,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6708,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>2104</v>
+        <v>2000</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -6726,7 +6746,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6744,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="H48">
-        <v>2105</v>
+        <v>2100</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6762,7 +6782,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6780,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -6798,7 +6818,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6816,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="H50">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6834,7 +6854,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6843,16 +6863,16 @@
         <v>6</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>2000</v>
+        <v>2103</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -6870,7 +6890,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6879,16 +6899,16 @@
         <v>6</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>2000</v>
+        <v>2104</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -6906,7 +6926,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6915,16 +6935,16 @@
         <v>6</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>2105</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -6942,7 +6962,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6951,16 +6971,16 @@
         <v>6</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>2106</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -6978,7 +6998,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6987,16 +7007,16 @@
         <v>6</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>2000</v>
+        <v>2107</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>
@@ -7014,7 +7034,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7026,10 +7046,10 @@
         <v>1</v>
       </c>
       <c r="F56">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G56">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H56">
         <v>2000</v>
@@ -7050,7 +7070,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7059,7 +7079,7 @@
         <v>6</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57">
         <v>5</v>
@@ -7068,7 +7088,7 @@
         <v>2</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -7086,7 +7106,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7095,13 +7115,13 @@
         <v>6</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -7122,7 +7142,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7131,16 +7151,16 @@
         <v>6</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -7158,7 +7178,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7167,13 +7187,13 @@
         <v>6</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60">
         <v>2000</v>
@@ -7194,7 +7214,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7203,13 +7223,13 @@
         <v>6</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H61">
         <v>2000</v>
@@ -7230,7 +7250,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7242,13 +7262,13 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -7257,6 +7277,186 @@
         <v>100</v>
       </c>
       <c r="K62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>2061</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>6</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>100</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>2062</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>6</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>2000</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>100</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>2063</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>6</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>2000</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>100</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>2064</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>6</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>2000</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>100</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>2065</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>6</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>2000</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>100</v>
+      </c>
+      <c r="K67">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5B8391-2CDA-459F-A15A-BAA05D03FF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01A7C73-92A4-42CF-AB8F-AD05C3A135DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="960" windowWidth="25560" windowHeight="14355" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="1050" windowWidth="25560" windowHeight="14355" tabRatio="804" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -5108,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -5246,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -5288,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -5324,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -8799,7 +8799,7 @@
         <v>75</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01A7C73-92A4-42CF-AB8F-AD05C3A135DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8B7B76-983B-4258-BEDF-7DFC7BEC4E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="1050" windowWidth="25560" windowHeight="14355" tabRatio="804" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="1140" windowWidth="25560" windowHeight="14355" tabRatio="804" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -6548,7 +6548,7 @@
         <v>2</v>
       </c>
       <c r="H42">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6584,7 +6584,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6620,7 +6620,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6728,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -6764,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="H48">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6800,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="H50">
-        <v>2102</v>
+        <v>0</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="H51">
-        <v>2103</v>
+        <v>0</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -6908,7 +6908,7 @@
         <v>1</v>
       </c>
       <c r="H52">
-        <v>2104</v>
+        <v>0</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -6944,7 +6944,7 @@
         <v>1</v>
       </c>
       <c r="H53">
-        <v>2105</v>
+        <v>0</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>1</v>
       </c>
       <c r="H54">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -7016,7 +7016,7 @@
         <v>1</v>
       </c>
       <c r="H55">
-        <v>2107</v>
+        <v>0</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8B7B76-983B-4258-BEDF-7DFC7BEC4E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92D1B0A-93B3-4BEB-9237-2F1052092D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2925" yWindow="1140" windowWidth="25560" windowHeight="14355" tabRatio="804" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7226,10 +7226,10 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G61">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H61">
         <v>2000</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92D1B0A-93B3-4BEB-9237-2F1052092D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69716C44-1601-4767-9B37-6AB0D2914826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="1140" windowWidth="25560" windowHeight="14355" tabRatio="804" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3225" yWindow="1125" windowWidth="25560" windowHeight="14355" tabRatio="804" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="213">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -7469,7 +7469,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DBDC14-7E25-4116-BA5C-8148F52CCF05}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9857,7 +9857,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
-        <f t="shared" ref="A67:A74" si="2">ROW()-2+10000</f>
+        <f t="shared" ref="A67:A75" si="2">ROW()-2+10000</f>
         <v>10065</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -9897,7 +9897,7 @@
         <v>10066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -9909,10 +9909,10 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G68">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -9921,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -9933,7 +9933,7 @@
         <v>10067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>27</v>
+        <v>193</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -9945,10 +9945,10 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>10000</v>
+        <v>600</v>
       </c>
       <c r="G69">
-        <v>5000</v>
+        <v>300</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -9969,7 +9969,7 @@
         <v>10068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -9981,10 +9981,10 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G70">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -10005,7 +10005,7 @@
         <v>10069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -10017,10 +10017,10 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G71">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -10041,7 +10041,7 @@
         <v>10070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -10053,10 +10053,10 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G72">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -10077,7 +10077,7 @@
         <v>10071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -10089,10 +10089,10 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G73">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -10113,7 +10113,7 @@
         <v>10072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -10125,13 +10125,13 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G74">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -10140,6 +10140,42 @@
         <v>1000</v>
       </c>
       <c r="K74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <f t="shared" si="2"/>
+        <v>10073</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>700</v>
+      </c>
+      <c r="G75">
+        <v>350</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1000</v>
+      </c>
+      <c r="K75">
         <v>1</v>
       </c>
     </row>
@@ -11050,7 +11086,7 @@
         <v>150</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69716C44-1601-4767-9B37-6AB0D2914826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCFAB18-9307-446E-AA48-C0D490B06CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="1125" windowWidth="25560" windowHeight="14355" tabRatio="804" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="930" windowWidth="25560" windowHeight="14370" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -11378,7 +11378,7 @@
         <v>171</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -11387,7 +11387,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="G2">
         <v>15</v>
@@ -11486,7 +11486,7 @@
         <v>172</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -11501,7 +11501,7 @@
         <v>35</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCFAB18-9307-446E-AA48-C0D490B06CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC2B8C2-3C5F-4ED8-A6CE-E1DF69F8E8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="930" windowWidth="25560" windowHeight="14370" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="1245" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="214">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -887,6 +887,10 @@
   </si>
   <si>
     <t>PatissierHat_Acce</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_timemagic_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5039,7 +5043,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5122,7 +5126,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A67" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A68" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -6041,7 +6045,7 @@
         <v>3</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -6062,22 +6066,22 @@
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="C29">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
         <v>2</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -6098,7 +6102,7 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C30">
         <v>50</v>
@@ -6134,7 +6138,7 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31">
         <v>50</v>
@@ -6170,7 +6174,7 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C32">
         <v>50</v>
@@ -6179,7 +6183,7 @@
         <v>3</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -6188,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -6206,7 +6210,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C33">
         <v>50</v>
@@ -6242,7 +6246,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34">
         <v>50</v>
@@ -6278,7 +6282,7 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C35">
         <v>50</v>
@@ -6287,7 +6291,7 @@
         <v>3</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <v>2</v>
@@ -6296,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6314,25 +6318,25 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -6350,7 +6354,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6362,10 +6366,10 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -6386,7 +6390,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6398,13 +6402,13 @@
         <v>0</v>
       </c>
       <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38">
         <v>5</v>
       </c>
-      <c r="G38">
-        <v>2</v>
-      </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -6422,7 +6426,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -6434,13 +6438,13 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6458,7 +6462,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -6470,13 +6474,13 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6494,10 +6498,10 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -6506,10 +6510,10 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -6530,25 +6534,25 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D42">
         <v>6</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6566,7 +6570,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6575,13 +6579,13 @@
         <v>6</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -6602,7 +6606,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6638,7 +6642,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6674,7 +6678,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6710,7 +6714,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6746,7 +6750,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6782,7 +6786,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6818,7 +6822,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6854,7 +6858,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6890,7 +6894,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6926,7 +6930,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6962,7 +6966,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6998,7 +7002,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7034,7 +7038,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7043,16 +7047,16 @@
         <v>6</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -7070,7 +7074,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7106,7 +7110,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7118,13 +7122,13 @@
         <v>1</v>
       </c>
       <c r="F58">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -7142,7 +7146,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7154,10 +7158,10 @@
         <v>1</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -7178,7 +7182,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7196,7 +7200,7 @@
         <v>2</v>
       </c>
       <c r="H60">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -7214,7 +7218,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7226,10 +7230,10 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H61">
         <v>2000</v>
@@ -7250,7 +7254,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7259,16 +7263,16 @@
         <v>6</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62">
+        <v>10</v>
+      </c>
+      <c r="G62">
         <v>5</v>
       </c>
-      <c r="G62">
-        <v>2</v>
-      </c>
       <c r="H62">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -7286,7 +7290,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7322,7 +7326,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7334,13 +7338,13 @@
         <v>0</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -7358,7 +7362,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7394,7 +7398,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7430,7 +7434,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7457,6 +7461,42 @@
         <v>100</v>
       </c>
       <c r="K67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>2066</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>6</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>2000</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>100</v>
+      </c>
+      <c r="K68">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC2B8C2-3C5F-4ED8-A6CE-E1DF69F8E8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D3E90C-EE06-43D1-AEDE-4AA07050EA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="1245" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="930" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="215">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -891,6 +891,10 @@
   </si>
   <si>
     <t>mg_timemagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_chocolatemagic_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10228,7 +10232,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -10816,7 +10820,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" ref="A17:A31" si="2">ROW()-2+20000</f>
+        <f t="shared" ref="A17:A32" si="2">ROW()-2+20000</f>
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -11252,7 +11256,7 @@
         <v>20027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -11264,13 +11268,13 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="G29">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -11288,7 +11292,7 @@
         <v>20028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -11300,10 +11304,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="G30">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -11324,7 +11328,7 @@
         <v>20029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -11336,10 +11340,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G31">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -11351,6 +11355,42 @@
         <v>1010</v>
       </c>
       <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f t="shared" si="2"/>
+        <v>20030</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>3000</v>
+      </c>
+      <c r="G32">
+        <v>1500</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1010</v>
+      </c>
+      <c r="K32">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D3E90C-EE06-43D1-AEDE-4AA07050EA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC61DCC-A2A1-4625-B2A9-72CE9084DDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="930" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1965" yWindow="1215" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="216">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -895,6 +895,10 @@
   </si>
   <si>
     <t>mg_chocolatemagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hikari_speed_up2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5047,7 +5051,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5130,7 +5134,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A68" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A69" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7126,7 +7130,7 @@
         <v>1</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58">
         <v>2</v>
@@ -7150,7 +7154,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7162,13 +7166,13 @@
         <v>1</v>
       </c>
       <c r="F59">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -7186,7 +7190,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7198,10 +7202,10 @@
         <v>1</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -7222,7 +7226,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7240,7 +7244,7 @@
         <v>2</v>
       </c>
       <c r="H61">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -7258,7 +7262,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7270,10 +7274,10 @@
         <v>1</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H62">
         <v>2000</v>
@@ -7294,7 +7298,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7303,16 +7307,16 @@
         <v>6</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63">
+        <v>10</v>
+      </c>
+      <c r="G63">
         <v>5</v>
       </c>
-      <c r="G63">
-        <v>2</v>
-      </c>
       <c r="H63">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
@@ -7330,7 +7334,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7366,7 +7370,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7378,13 +7382,13 @@
         <v>0</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -7402,7 +7406,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7438,7 +7442,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7474,7 +7478,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7501,6 +7505,42 @@
         <v>100</v>
       </c>
       <c r="K68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>2067</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>6</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>3</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>2000</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>100</v>
+      </c>
+      <c r="K69">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC61DCC-A2A1-4625-B2A9-72CE9084DDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A409FD-F49A-4B66-9D59-6250DD436EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="1215" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="216">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -11443,7 +11443,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11491,7 +11491,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A34" si="0">ROW()-2+30000</f>
+        <f t="shared" ref="A2:A35" si="0">ROW()-2+30000</f>
         <v>30000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -12539,7 +12539,7 @@
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -12551,19 +12551,19 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G31">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -12575,7 +12575,7 @@
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -12593,7 +12593,7 @@
         <v>250</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -12611,7 +12611,7 @@
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -12623,10 +12623,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G33">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -12647,7 +12647,7 @@
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -12659,13 +12659,13 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>2800</v>
+        <v>700</v>
       </c>
       <c r="G34">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -12674,6 +12674,42 @@
         <v>1020</v>
       </c>
       <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>30033</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>2800</v>
+      </c>
+      <c r="G35">
+        <v>1400</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1020</v>
+      </c>
+      <c r="K35">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A409FD-F49A-4B66-9D59-6250DD436EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C017C1D6-F203-41B4-A977-95AF0C50C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="1140" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="220">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -899,6 +899,22 @@
   </si>
   <si>
     <t>hikari_speed_up2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_parfect_princess_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_epiclesis_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_latria_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_three_stars_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5051,7 +5067,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5134,7 +5150,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A69" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A73" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -6110,19 +6126,19 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="C30">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -6146,19 +6162,19 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>113</v>
+        <v>217</v>
       </c>
       <c r="C31">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -6182,19 +6198,19 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="C32">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -6218,25 +6234,25 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>115</v>
+        <v>219</v>
       </c>
       <c r="C33">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -6254,7 +6270,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C34">
         <v>50</v>
@@ -6263,7 +6279,7 @@
         <v>3</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -6272,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6290,7 +6306,7 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C35">
         <v>50</v>
@@ -6299,7 +6315,7 @@
         <v>3</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>2</v>
@@ -6308,7 +6324,7 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6326,7 +6342,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C36">
         <v>50</v>
@@ -6362,19 +6378,19 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -6398,22 +6414,22 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -6434,25 +6450,25 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6470,25 +6486,25 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6506,7 +6522,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -6518,13 +6534,13 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6542,10 +6558,10 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>6</v>
@@ -6554,13 +6570,13 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6578,7 +6594,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6587,7 +6603,7 @@
         <v>6</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -6596,7 +6612,7 @@
         <v>2</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6614,7 +6630,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6629,7 +6645,7 @@
         <v>3</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -6650,7 +6666,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6662,13 +6678,13 @@
         <v>0</v>
       </c>
       <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45">
         <v>3</v>
       </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6686,10 +6702,10 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D46">
         <v>6</v>
@@ -6698,13 +6714,13 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6722,7 +6738,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6731,13 +6747,13 @@
         <v>6</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -6758,7 +6774,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6794,7 +6810,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6830,7 +6846,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6866,7 +6882,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6902,7 +6918,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6938,7 +6954,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6974,7 +6990,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -7010,7 +7026,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7046,7 +7062,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7082,7 +7098,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7091,16 +7107,16 @@
         <v>6</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -7118,7 +7134,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7127,16 +7143,16 @@
         <v>6</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -7154,7 +7170,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7163,16 +7179,16 @@
         <v>6</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -7190,7 +7206,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7199,13 +7215,13 @@
         <v>6</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -7226,7 +7242,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7238,13 +7254,13 @@
         <v>1</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61">
         <v>2</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -7262,7 +7278,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7298,7 +7314,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7310,10 +7326,10 @@
         <v>1</v>
       </c>
       <c r="F63">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H63">
         <v>2000</v>
@@ -7334,7 +7350,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7343,13 +7359,13 @@
         <v>6</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -7370,7 +7386,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7379,10 +7395,10 @@
         <v>6</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -7406,7 +7422,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7415,13 +7431,13 @@
         <v>6</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66">
         <v>2000</v>
@@ -7442,7 +7458,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7451,13 +7467,13 @@
         <v>6</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H67">
         <v>2000</v>
@@ -7478,7 +7494,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7490,13 +7506,13 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -7514,7 +7530,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7526,13 +7542,13 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -7541,6 +7557,150 @@
         <v>100</v>
       </c>
       <c r="K69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <f t="shared" si="0"/>
+        <v>2068</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>6</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>2000</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>100</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <f t="shared" si="0"/>
+        <v>2069</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>6</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>2000</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>100</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <f t="shared" si="0"/>
+        <v>2070</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>3</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>2000</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>100</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <f t="shared" si="0"/>
+        <v>2071</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>6</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>3</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>2000</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>100</v>
+      </c>
+      <c r="K73">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C017C1D6-F203-41B4-A977-95AF0C50C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AB76DF-04DA-41AA-B3E3-F63CB9D8E7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1140" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2850" yWindow="1380" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="222">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -890,10 +890,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>mg_timemagic_book</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>mg_chocolatemagic_book</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -915,6 +911,18 @@
   </si>
   <si>
     <t>mg_three_stars_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_starmagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_night_barron_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_crescent_moon_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5067,7 +5075,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5150,7 +5158,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A73" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A75" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -6090,7 +6098,7 @@
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6126,7 +6134,7 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -6138,7 +6146,7 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -6162,7 +6170,7 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6174,7 +6182,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -6198,7 +6206,7 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6210,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -6234,7 +6242,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6246,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -6270,19 +6278,19 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="C34">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -6306,25 +6314,25 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>113</v>
+        <v>218</v>
       </c>
       <c r="C35">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6342,7 +6350,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C36">
         <v>50</v>
@@ -6378,7 +6386,7 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C37">
         <v>50</v>
@@ -6387,7 +6395,7 @@
         <v>3</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -6396,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6414,7 +6422,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C38">
         <v>50</v>
@@ -6423,7 +6431,7 @@
         <v>3</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>2</v>
@@ -6432,7 +6440,7 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -6450,7 +6458,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C39">
         <v>50</v>
@@ -6486,7 +6494,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -6495,7 +6503,7 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>2</v>
@@ -6504,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6522,19 +6530,19 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -6558,25 +6566,25 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6594,7 +6602,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -6606,13 +6614,13 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6630,7 +6638,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6642,10 +6650,10 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -6666,7 +6674,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6678,10 +6686,10 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -6702,10 +6710,10 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>194</v>
+        <v>64</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>6</v>
@@ -6714,13 +6722,13 @@
         <v>0</v>
       </c>
       <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46">
         <v>2</v>
       </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
       <c r="H46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6738,7 +6746,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6747,16 +6755,16 @@
         <v>6</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -6774,10 +6782,10 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <v>6</v>
@@ -6786,13 +6794,13 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6810,7 +6818,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6819,13 +6827,13 @@
         <v>6</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -6846,7 +6854,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6882,7 +6890,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6918,7 +6926,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6954,7 +6962,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6990,7 +6998,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -7026,7 +7034,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7062,7 +7070,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7098,7 +7106,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7134,7 +7142,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7170,7 +7178,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7206,7 +7214,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7242,7 +7250,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7251,16 +7259,16 @@
         <v>6</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -7278,7 +7286,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7287,16 +7295,16 @@
         <v>6</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -7314,7 +7322,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7326,10 +7334,10 @@
         <v>1</v>
       </c>
       <c r="F63">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H63">
         <v>2000</v>
@@ -7350,7 +7358,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7362,13 +7370,13 @@
         <v>1</v>
       </c>
       <c r="F64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -7386,7 +7394,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7398,13 +7406,13 @@
         <v>1</v>
       </c>
       <c r="F65">
+        <v>8</v>
+      </c>
+      <c r="G65">
         <v>4</v>
       </c>
-      <c r="G65">
-        <v>2</v>
-      </c>
       <c r="H65">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -7422,7 +7430,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7434,13 +7442,13 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -7458,7 +7466,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7470,13 +7478,13 @@
         <v>1</v>
       </c>
       <c r="F67">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -7494,7 +7502,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7503,16 +7511,16 @@
         <v>6</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -7530,7 +7538,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7539,16 +7547,16 @@
         <v>6</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69">
+        <v>10</v>
+      </c>
+      <c r="G69">
         <v>5</v>
       </c>
-      <c r="G69">
-        <v>2</v>
-      </c>
       <c r="H69">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -7566,7 +7574,7 @@
         <v>2068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7578,13 +7586,13 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="b">
         <v>0</v>
@@ -7602,7 +7610,7 @@
         <v>2069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7614,13 +7622,13 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -7638,7 +7646,7 @@
         <v>2070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7674,7 +7682,7 @@
         <v>2071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7701,6 +7709,78 @@
         <v>100</v>
       </c>
       <c r="K73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <f t="shared" si="0"/>
+        <v>2072</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>6</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>2000</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>100</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <f t="shared" si="0"/>
+        <v>2073</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>6</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>2000</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>100</v>
+      </c>
+      <c r="K75">
         <v>1</v>
       </c>
     </row>
@@ -11456,7 +11536,7 @@
         <v>20027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C29">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AB76DF-04DA-41AA-B3E3-F63CB9D8E7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA229EE3-CCA2-40DE-B72A-A647ABAE2E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="1380" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="1170" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -5138,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -5174,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -5210,7 +5210,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -5246,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -5282,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -5390,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -5426,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -5534,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -6152,7 +6152,7 @@
         <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -6215,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -6251,7 +6251,7 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -6287,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -6323,7 +6323,7 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <v>15</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA229EE3-CCA2-40DE-B72A-A647ABAE2E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6216CF-720F-48A7-8C75-F7E33E624BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="1170" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="525" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -6755,7 +6755,7 @@
         <v>6</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
         <v>6</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6216CF-720F-48A7-8C75-F7E33E624BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F231C066-FA95-4BBA-81DA-9F1425836165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="525" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="870" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="225">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -923,6 +923,18 @@
   </si>
   <si>
     <t>mg_crescent_moon_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_lightning_grape_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_dreamy_sapphire_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>whisk_magic</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5075,7 +5087,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5158,7 +5170,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A75" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A77" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -6188,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -6296,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6350,19 +6362,19 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="C36">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
         <v>3</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -6386,19 +6398,19 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>113</v>
+        <v>223</v>
       </c>
       <c r="C37">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -6422,7 +6434,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C38">
         <v>50</v>
@@ -6458,7 +6470,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C39">
         <v>50</v>
@@ -6467,7 +6479,7 @@
         <v>3</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -6476,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -6494,7 +6506,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -6503,7 +6515,7 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>2</v>
@@ -6512,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6530,7 +6542,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C41">
         <v>50</v>
@@ -6566,7 +6578,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C42">
         <v>50</v>
@@ -6575,7 +6587,7 @@
         <v>3</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>2</v>
@@ -6584,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -6602,19 +6614,19 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -6638,25 +6650,25 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6674,7 +6686,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6686,13 +6698,13 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6710,7 +6722,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6722,10 +6734,10 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -6746,7 +6758,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6755,13 +6767,13 @@
         <v>6</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -6782,10 +6794,10 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>194</v>
+        <v>64</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>6</v>
@@ -6794,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
         <v>2</v>
       </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6818,7 +6830,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6830,13 +6842,13 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -6854,10 +6866,10 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D50">
         <v>6</v>
@@ -6866,13 +6878,13 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6890,7 +6902,7 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6899,13 +6911,13 @@
         <v>6</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -6926,7 +6938,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6962,7 +6974,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6998,7 +7010,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -7034,7 +7046,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7070,7 +7082,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7106,7 +7118,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7142,7 +7154,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7178,7 +7190,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7214,7 +7226,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7250,7 +7262,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7286,7 +7298,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7322,7 +7334,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7331,16 +7343,16 @@
         <v>6</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
@@ -7358,7 +7370,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7367,16 +7379,16 @@
         <v>6</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -7394,7 +7406,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7406,10 +7418,10 @@
         <v>1</v>
       </c>
       <c r="F65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H65">
         <v>2000</v>
@@ -7430,7 +7442,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7442,13 +7454,13 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -7466,7 +7478,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7478,13 +7490,13 @@
         <v>1</v>
       </c>
       <c r="F67">
+        <v>8</v>
+      </c>
+      <c r="G67">
         <v>4</v>
       </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
       <c r="H67">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -7502,7 +7514,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7514,13 +7526,13 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -7538,7 +7550,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7550,13 +7562,13 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G69">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -7574,7 +7586,7 @@
         <v>2068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7583,16 +7595,16 @@
         <v>6</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I70" t="b">
         <v>0</v>
@@ -7610,7 +7622,7 @@
         <v>2069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7619,16 +7631,16 @@
         <v>6</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71">
+        <v>10</v>
+      </c>
+      <c r="G71">
         <v>5</v>
       </c>
-      <c r="G71">
-        <v>2</v>
-      </c>
       <c r="H71">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -7646,7 +7658,7 @@
         <v>2070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7658,13 +7670,13 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I72" t="b">
         <v>0</v>
@@ -7682,7 +7694,7 @@
         <v>2071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7694,13 +7706,13 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -7718,7 +7730,7 @@
         <v>2072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7754,7 +7766,7 @@
         <v>2073</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7781,6 +7793,78 @@
         <v>100</v>
       </c>
       <c r="K75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <f t="shared" si="0"/>
+        <v>2074</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>6</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>2000</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>100</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <f t="shared" si="0"/>
+        <v>2075</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>6</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>2000</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>100</v>
+      </c>
+      <c r="K77">
         <v>1</v>
       </c>
     </row>
@@ -10512,7 +10596,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -10740,7 +10824,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" ref="A7:A16" si="1">ROW()-2+20000</f>
+        <f t="shared" ref="A7:A17" si="1">ROW()-2+20000</f>
         <v>20005</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -10960,7 +11044,7 @@
         <v>20011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>224</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -10972,10 +11056,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="G13">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -10996,7 +11080,7 @@
         <v>20012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -11008,10 +11092,10 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <v>1500</v>
+      </c>
+      <c r="G14">
         <v>500</v>
-      </c>
-      <c r="G14">
-        <v>250</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -11032,7 +11116,7 @@
         <v>20013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -11068,19 +11152,19 @@
         <v>20014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G16">
         <v>250</v>
@@ -11100,26 +11184,26 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" ref="A17:A32" si="2">ROW()-2+20000</f>
+        <f t="shared" si="1"/>
         <v>20015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="G17">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -11136,11 +11220,11 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A18:A33" si="2">ROW()-2+20000</f>
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -11152,10 +11236,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G18">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -11176,7 +11260,7 @@
         <v>20017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>179</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -11188,10 +11272,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G19">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -11212,7 +11296,7 @@
         <v>20018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -11224,10 +11308,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="G20">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -11248,7 +11332,7 @@
         <v>20019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -11260,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="G21">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -11284,7 +11368,7 @@
         <v>20020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -11296,10 +11380,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="G22">
-        <v>1500</v>
+        <v>150</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -11320,7 +11404,7 @@
         <v>20021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -11332,10 +11416,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="G23">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -11356,7 +11440,7 @@
         <v>20022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -11368,10 +11452,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="G24">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -11392,7 +11476,7 @@
         <v>20023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -11410,7 +11494,7 @@
         <v>150</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -11428,7 +11512,7 @@
         <v>20024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -11440,10 +11524,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G26">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -11464,7 +11548,7 @@
         <v>20025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -11500,7 +11584,7 @@
         <v>20026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -11512,13 +11596,13 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G28">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -11536,7 +11620,7 @@
         <v>20027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -11548,10 +11632,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G29">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -11572,7 +11656,7 @@
         <v>20028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -11584,10 +11668,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="G30">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -11608,7 +11692,7 @@
         <v>20029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -11620,10 +11704,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="G31">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -11644,7 +11728,7 @@
         <v>20030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -11656,10 +11740,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G32">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -11671,6 +11755,42 @@
         <v>1010</v>
       </c>
       <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <f t="shared" si="2"/>
+        <v>20031</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>3000</v>
+      </c>
+      <c r="G33">
+        <v>1500</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1010</v>
+      </c>
+      <c r="K33">
         <v>1</v>
       </c>
     </row>
@@ -13248,7 +13368,7 @@
         <v>25000</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F231C066-FA95-4BBA-81DA-9F1425836165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1414F4B-747F-4EEC-9504-B64BDF5D9B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="870" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -6371,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>3</v>
@@ -6410,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -12917,7 +12917,7 @@
         <v>400</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -13656,7 +13656,7 @@
         <v>400</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1414F4B-747F-4EEC-9504-B64BDF5D9B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60E89D8-840D-454A-91A1-C6BF1EAF79F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="1125" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -5942,10 +5942,10 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -6410,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -7418,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -11056,10 +11056,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1300</v>
+        <v>2500</v>
       </c>
       <c r="G13">
-        <v>750</v>
+        <v>1250</v>
       </c>
       <c r="H13">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60E89D8-840D-454A-91A1-C6BF1EAF79F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0849FAF-E388-4CEF-A9E9-5DB4EDD33F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="1125" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="825" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="232">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -935,6 +935,34 @@
   </si>
   <si>
     <t>whisk_magic</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>forgetmenot_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_moonlight_banana_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hikari_powerup3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>candy_powerup1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tea_powerup4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>crepe_powerup4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shokukan_powerup3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5087,7 +5115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5170,7 +5198,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A77" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A81" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5867,10 +5895,10 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -5903,10 +5931,10 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -6230,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -6263,10 +6291,10 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -6302,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -6410,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -6434,22 +6462,22 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
+        <v>226</v>
       </c>
       <c r="C38">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
         <v>3</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>2</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -6470,7 +6498,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39">
         <v>50</v>
@@ -6506,7 +6534,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -6542,7 +6570,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C41">
         <v>50</v>
@@ -6551,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -6560,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6578,7 +6606,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C42">
         <v>50</v>
@@ -6614,7 +6642,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C43">
         <v>50</v>
@@ -6650,7 +6678,7 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C44">
         <v>50</v>
@@ -6659,7 +6687,7 @@
         <v>3</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -6668,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6686,25 +6714,25 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6722,7 +6750,7 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6734,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -6758,7 +6786,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6770,13 +6798,13 @@
         <v>0</v>
       </c>
       <c r="F47">
+        <v>10</v>
+      </c>
+      <c r="G47">
         <v>5</v>
       </c>
-      <c r="G47">
-        <v>2</v>
-      </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -6794,7 +6822,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6806,13 +6834,13 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G48">
         <v>2</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6830,7 +6858,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6839,16 +6867,16 @@
         <v>6</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -6866,22 +6894,22 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>6</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -6902,25 +6930,25 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D51">
         <v>6</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -6938,7 +6966,7 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6947,13 +6975,13 @@
         <v>6</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -6974,7 +7002,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -7010,7 +7038,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -7046,7 +7074,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7082,7 +7110,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7118,7 +7146,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7154,7 +7182,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7190,7 +7218,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7226,7 +7254,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7262,7 +7290,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7298,7 +7326,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7334,7 +7362,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7370,7 +7398,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7406,7 +7434,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7415,16 +7443,16 @@
         <v>6</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>3</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -7442,7 +7470,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7454,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66">
         <v>2</v>
@@ -7478,7 +7506,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7490,10 +7518,10 @@
         <v>1</v>
       </c>
       <c r="F67">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H67">
         <v>2000</v>
@@ -7514,7 +7542,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7526,13 +7554,13 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -7550,7 +7578,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7562,10 +7590,10 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -7586,7 +7614,7 @@
         <v>2068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7604,7 +7632,7 @@
         <v>2</v>
       </c>
       <c r="H70">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="b">
         <v>0</v>
@@ -7622,7 +7650,7 @@
         <v>2069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7634,10 +7662,10 @@
         <v>1</v>
       </c>
       <c r="F71">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H71">
         <v>2000</v>
@@ -7658,7 +7686,7 @@
         <v>2070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7667,16 +7695,16 @@
         <v>6</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
+        <v>10</v>
+      </c>
+      <c r="G72">
         <v>5</v>
       </c>
-      <c r="G72">
-        <v>2</v>
-      </c>
       <c r="H72">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I72" t="b">
         <v>0</v>
@@ -7694,7 +7722,7 @@
         <v>2071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7730,7 +7758,7 @@
         <v>2072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7742,13 +7770,13 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -7766,7 +7794,7 @@
         <v>2073</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7802,7 +7830,7 @@
         <v>2074</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7814,10 +7842,10 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76">
         <v>2000</v>
@@ -7838,7 +7866,7 @@
         <v>2075</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7865,6 +7893,150 @@
         <v>100</v>
       </c>
       <c r="K77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <f t="shared" si="0"/>
+        <v>2076</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>6</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>2000</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>100</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <f t="shared" si="0"/>
+        <v>2077</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>6</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>5</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>2000</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>100</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <f t="shared" si="0"/>
+        <v>2078</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>6</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>2000</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>100</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <f t="shared" si="0"/>
+        <v>2079</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>6</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>2000</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>100</v>
+      </c>
+      <c r="K81">
         <v>1</v>
       </c>
     </row>
@@ -13082,7 +13254,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4060CA39-02FB-4508-8603-5A906A5C9777}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -13130,7 +13302,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A18" si="0">ROW()-2+40000</f>
+        <f t="shared" ref="A2:A20" si="0">ROW()-2+40000</f>
         <v>40000</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -13494,7 +13666,7 @@
         <v>40010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>230</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -13506,13 +13678,13 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="G12">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -13530,7 +13702,7 @@
         <v>40011</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -13542,13 +13714,13 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="G13">
-        <v>2500</v>
+        <v>2750</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -13566,7 +13738,7 @@
         <v>40012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -13578,10 +13750,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="G14">
-        <v>3750</v>
+        <v>2500</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -13602,22 +13774,22 @@
         <v>40013</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>800</v>
+        <v>7500</v>
       </c>
       <c r="G15">
-        <v>400</v>
+        <v>3750</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -13638,7 +13810,7 @@
         <v>40014</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -13656,7 +13828,7 @@
         <v>400</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -13674,7 +13846,7 @@
         <v>40015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -13686,10 +13858,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>10000</v>
+        <v>800</v>
       </c>
       <c r="G17">
-        <v>5000</v>
+        <v>400</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -13710,7 +13882,7 @@
         <v>40016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -13722,10 +13894,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="G18">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -13742,11 +13914,11 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f t="shared" ref="A19" si="1">ROW()-2+40000</f>
+        <f t="shared" si="0"/>
         <v>40017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -13758,13 +13930,13 @@
         <v>0</v>
       </c>
       <c r="F19">
+        <v>10000</v>
+      </c>
+      <c r="G19">
         <v>5000</v>
       </c>
-      <c r="G19">
-        <v>2500</v>
-      </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -13773,6 +13945,78 @@
         <v>1030</v>
       </c>
       <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>40018</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>500</v>
+      </c>
+      <c r="G20">
+        <v>300</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1030</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f t="shared" ref="A21" si="1">ROW()-2+40000</f>
+        <v>40019</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>5000</v>
+      </c>
+      <c r="G21">
+        <v>2500</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1030</v>
+      </c>
+      <c r="K21">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0849FAF-E388-4CEF-A9E9-5DB4EDD33F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9474D8-A074-4589-8109-795EF007B0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="825" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="945" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -5742,25 +5742,25 @@
         <v>2016</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
         <v>2</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
       <c r="H18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -5778,25 +5778,25 @@
         <v>2017</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
         <v>2</v>
       </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
       <c r="H19">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -5814,7 +5814,7 @@
         <v>2018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -5829,10 +5829,10 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>2019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -5865,7 +5865,7 @@
         <v>5</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -5886,7 +5886,7 @@
         <v>2020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -5895,13 +5895,13 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -5922,7 +5922,7 @@
         <v>2021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -5931,13 +5931,13 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -5958,7 +5958,7 @@
         <v>2022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -5970,10 +5970,10 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -5994,7 +5994,7 @@
         <v>2023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -6003,13 +6003,13 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -6030,7 +6030,7 @@
         <v>2024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -6045,7 +6045,7 @@
         <v>3</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -6066,7 +6066,7 @@
         <v>2025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -6075,13 +6075,13 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>2026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -6114,13 +6114,13 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -6138,7 +6138,7 @@
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6150,13 +6150,13 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -6186,13 +6186,13 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -6210,7 +6210,7 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6219,16 +6219,16 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -6246,7 +6246,7 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6258,13 +6258,13 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -6282,7 +6282,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6291,16 +6291,16 @@
         <v>1</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -6318,7 +6318,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6327,16 +6327,16 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6354,7 +6354,7 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6366,13 +6366,13 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6399,13 +6399,13 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36">
         <v>3</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -6426,16 +6426,16 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -6462,22 +6462,22 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -6498,7 +6498,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C39">
         <v>50</v>
@@ -6534,7 +6534,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -6543,7 +6543,7 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>2</v>
@@ -6552,7 +6552,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6570,7 +6570,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C41">
         <v>50</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -6588,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -6606,7 +6606,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C42">
         <v>50</v>
@@ -6642,7 +6642,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C43">
         <v>50</v>
@@ -6651,7 +6651,7 @@
         <v>3</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -6660,7 +6660,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6678,16 +6678,16 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C44">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D44">
         <v>3</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -6696,7 +6696,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6714,16 +6714,16 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C45">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45">
         <v>2</v>
@@ -6732,7 +6732,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9474D8-A074-4589-8109-795EF007B0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4772F394-E2C8-4D3E-A957-705E58514C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="945" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="705" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -11588,10 +11588,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="G23">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -11624,10 +11624,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G24">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>5500</v>
+        <v>10000</v>
       </c>
       <c r="G13">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="H13">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4772F394-E2C8-4D3E-A957-705E58514C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A71F1E-8694-4815-A94E-661F85D2AB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="705" windowWidth="25485" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -13678,10 +13678,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>4800</v>
+        <v>48000</v>
       </c>
       <c r="G12">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="H12">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A71F1E-8694-4815-A94E-661F85D2AB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888FA4AF-AF15-4C60-92FF-D21C4A96DED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1125" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="233">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -963,6 +963,10 @@
   </si>
   <si>
     <t>shokukan_powerup3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>infinity_fountain_tansan</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5115,7 +5119,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5198,7 +5202,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A81" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A82" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7470,7 +7474,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7479,13 +7483,13 @@
         <v>6</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H66">
         <v>2000</v>
@@ -7506,7 +7510,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7518,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67">
         <v>2</v>
@@ -7542,7 +7546,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7554,10 +7558,10 @@
         <v>1</v>
       </c>
       <c r="F68">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H68">
         <v>2000</v>
@@ -7578,7 +7582,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7590,13 +7594,13 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -7614,7 +7618,7 @@
         <v>2068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7626,10 +7630,10 @@
         <v>1</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -7650,7 +7654,7 @@
         <v>2069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7668,7 +7672,7 @@
         <v>2</v>
       </c>
       <c r="H71">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -7686,7 +7690,7 @@
         <v>2070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7698,10 +7702,10 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G72">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H72">
         <v>2000</v>
@@ -7722,7 +7726,7 @@
         <v>2071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7731,16 +7735,16 @@
         <v>6</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73">
+        <v>10</v>
+      </c>
+      <c r="G73">
         <v>5</v>
       </c>
-      <c r="G73">
-        <v>2</v>
-      </c>
       <c r="H73">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -7758,7 +7762,7 @@
         <v>2072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7794,7 +7798,7 @@
         <v>2073</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7806,13 +7810,13 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -7830,7 +7834,7 @@
         <v>2074</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7842,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76">
         <v>2000</v>
@@ -7866,7 +7870,7 @@
         <v>2075</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7878,10 +7882,10 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77">
         <v>2000</v>
@@ -7902,7 +7906,7 @@
         <v>2076</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7938,7 +7942,7 @@
         <v>2077</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>228</v>
+        <v>148</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7950,10 +7954,10 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>2000</v>
@@ -7974,7 +7978,7 @@
         <v>2078</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7986,10 +7990,10 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80">
         <v>2000</v>
@@ -8010,7 +8014,7 @@
         <v>2079</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -8022,10 +8026,10 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81">
         <v>2000</v>
@@ -8037,6 +8041,42 @@
         <v>100</v>
       </c>
       <c r="K81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <f t="shared" si="0"/>
+        <v>2080</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>6</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>6</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>2000</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>100</v>
+      </c>
+      <c r="K82">
         <v>1</v>
       </c>
     </row>
@@ -10501,7 +10541,7 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -13095,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="K31">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888FA4AF-AF15-4C60-92FF-D21C4A96DED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A3DD8E-4A56-4FB0-9011-BBF69E1994AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1125" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="735" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="238">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -967,6 +967,26 @@
   </si>
   <si>
     <t>infinity_fountain_tansan</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>monocle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_fire_ark_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_icemagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_windmagic_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mg_caramelized_book</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5119,7 +5139,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5202,7 +5222,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A82" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A84" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -6070,7 +6090,7 @@
         <v>2025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -6082,7 +6102,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -6106,7 +6126,7 @@
         <v>2026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -6118,13 +6138,13 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -6142,7 +6162,7 @@
         <v>2027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6178,7 +6198,7 @@
         <v>2028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -6190,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -6214,7 +6234,7 @@
         <v>2029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6223,10 +6243,10 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -6250,7 +6270,7 @@
         <v>2030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6259,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -6268,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -6286,7 +6306,7 @@
         <v>2031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6298,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -6322,7 +6342,7 @@
         <v>2032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6331,16 +6351,16 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -6358,7 +6378,7 @@
         <v>2033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6367,10 +6387,10 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -6394,7 +6414,7 @@
         <v>2034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6406,10 +6426,10 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -6430,25 +6450,25 @@
         <v>2035</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>112</v>
+        <v>226</v>
       </c>
       <c r="C37">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>7</v>
+      </c>
+      <c r="G37">
         <v>3</v>
       </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
       <c r="H37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -6466,7 +6486,7 @@
         <v>2036</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C38">
         <v>50</v>
@@ -6502,7 +6522,7 @@
         <v>2037</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C39">
         <v>50</v>
@@ -6538,7 +6558,7 @@
         <v>2038</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C40">
         <v>50</v>
@@ -6547,7 +6567,7 @@
         <v>3</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>2</v>
@@ -6556,7 +6576,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -6574,7 +6594,7 @@
         <v>2039</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41">
         <v>50</v>
@@ -6610,7 +6630,7 @@
         <v>2040</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C42">
         <v>50</v>
@@ -6646,7 +6666,7 @@
         <v>2041</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C43">
         <v>50</v>
@@ -6655,7 +6675,7 @@
         <v>3</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -6664,7 +6684,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -6682,10 +6702,10 @@
         <v>2042</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -6700,7 +6720,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -6718,7 +6738,7 @@
         <v>2043</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C45">
         <v>10</v>
@@ -6727,7 +6747,7 @@
         <v>3</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>2</v>
@@ -6736,7 +6756,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -6754,25 +6774,25 @@
         <v>2044</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -6790,7 +6810,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6802,10 +6822,10 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -6826,7 +6846,7 @@
         <v>2046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6838,13 +6858,13 @@
         <v>0</v>
       </c>
       <c r="F48">
+        <v>10</v>
+      </c>
+      <c r="G48">
         <v>5</v>
       </c>
-      <c r="G48">
-        <v>2</v>
-      </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -6862,7 +6882,7 @@
         <v>2047</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6874,13 +6894,13 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G49">
         <v>2</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -6898,7 +6918,7 @@
         <v>2048</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6907,16 +6927,16 @@
         <v>6</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6934,22 +6954,22 @@
         <v>2049</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>6</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -6970,25 +6990,25 @@
         <v>2050</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D52">
         <v>6</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -7006,7 +7026,7 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -7015,13 +7035,13 @@
         <v>6</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -7042,7 +7062,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -7078,7 +7098,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7114,7 +7134,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7150,7 +7170,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7186,7 +7206,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7222,7 +7242,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7258,7 +7278,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7294,7 +7314,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7330,7 +7350,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7366,7 +7386,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7402,7 +7422,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7438,7 +7458,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7474,7 +7494,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>232</v>
+        <v>137</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7486,13 +7506,13 @@
         <v>0</v>
       </c>
       <c r="F66">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -7510,7 +7530,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>141</v>
+        <v>233</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7522,13 +7542,13 @@
         <v>1</v>
       </c>
       <c r="F67">
+        <v>6</v>
+      </c>
+      <c r="G67">
         <v>3</v>
       </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
       <c r="H67">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -7546,7 +7566,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7555,13 +7575,13 @@
         <v>6</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H68">
         <v>2000</v>
@@ -7582,7 +7602,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7594,10 +7614,10 @@
         <v>1</v>
       </c>
       <c r="F69">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H69">
         <v>2000</v>
@@ -7618,7 +7638,7 @@
         <v>2068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7630,13 +7650,13 @@
         <v>1</v>
       </c>
       <c r="F70">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I70" t="b">
         <v>0</v>
@@ -7654,7 +7674,7 @@
         <v>2069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7666,13 +7686,13 @@
         <v>1</v>
       </c>
       <c r="F71">
+        <v>8</v>
+      </c>
+      <c r="G71">
         <v>4</v>
       </c>
-      <c r="G71">
-        <v>2</v>
-      </c>
       <c r="H71">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -7690,7 +7710,7 @@
         <v>2070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7702,13 +7722,13 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I72" t="b">
         <v>0</v>
@@ -7726,7 +7746,7 @@
         <v>2071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7738,13 +7758,13 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -7762,7 +7782,7 @@
         <v>2072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7771,16 +7791,16 @@
         <v>6</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -7798,7 +7818,7 @@
         <v>2073</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7807,16 +7827,16 @@
         <v>6</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75">
+        <v>10</v>
+      </c>
+      <c r="G75">
         <v>5</v>
       </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
       <c r="H75">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -7834,7 +7854,7 @@
         <v>2074</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7846,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
@@ -7870,7 +7890,7 @@
         <v>2075</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>227</v>
+        <v>139</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7882,13 +7902,13 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
@@ -7906,7 +7926,7 @@
         <v>2076</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7942,7 +7962,7 @@
         <v>2077</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7954,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>2000</v>
@@ -7978,7 +7998,7 @@
         <v>2078</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7990,10 +8010,10 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80">
         <v>2000</v>
@@ -8014,7 +8034,7 @@
         <v>2079</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -8050,7 +8070,7 @@
         <v>2080</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -8062,7 +8082,7 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82">
         <v>2</v>
@@ -8077,6 +8097,78 @@
         <v>100</v>
       </c>
       <c r="K82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <f t="shared" si="0"/>
+        <v>2081</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>2000</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>100</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <f t="shared" si="0"/>
+        <v>2082</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>6</v>
+      </c>
+      <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84">
+        <v>2000</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>100</v>
+      </c>
+      <c r="K84">
         <v>1</v>
       </c>
     </row>
@@ -10808,1213 +10900,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" customWidth="1"/>
-    <col min="10" max="11" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <f t="shared" ref="A2:A6" si="0">ROW()-2+20000</f>
-        <v>20000</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <v>15</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>1010</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <f t="shared" si="0"/>
-        <v>20001</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>1010</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <f t="shared" si="0"/>
-        <v>20002</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4">
-        <v>50</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>70</v>
-      </c>
-      <c r="G4">
-        <v>35</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>1010</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <f t="shared" si="0"/>
-        <v>20003</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>30</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>1010</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>20004</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>45</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>1010</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <f t="shared" ref="A7:A17" si="1">ROW()-2+20000</f>
-        <v>20005</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>30</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>1010</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <f t="shared" si="1"/>
-        <v>20006</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>20</v>
-      </c>
-      <c r="G8">
-        <v>15</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>1010</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <f t="shared" si="1"/>
-        <v>20007</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9">
-        <v>50</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>25</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>1010</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <f t="shared" si="1"/>
-        <v>20008</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10">
-        <v>50</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>30</v>
-      </c>
-      <c r="G10">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>1010</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <f t="shared" si="1"/>
-        <v>20009</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>50</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>1010</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <f t="shared" si="1"/>
-        <v>20010</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>2000</v>
-      </c>
-      <c r="G12">
-        <v>1000</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>1010</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <f t="shared" si="1"/>
-        <v>20011</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>2500</v>
-      </c>
-      <c r="G13">
-        <v>1250</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>1010</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <f t="shared" si="1"/>
-        <v>20012</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>1500</v>
-      </c>
-      <c r="G14">
-        <v>500</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>1010</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <f t="shared" si="1"/>
-        <v>20013</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>500</v>
-      </c>
-      <c r="G15">
-        <v>250</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>1010</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <f t="shared" si="1"/>
-        <v>20014</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>500</v>
-      </c>
-      <c r="G16">
-        <v>250</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>1010</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <f t="shared" si="1"/>
-        <v>20015</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>6</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>3000</v>
-      </c>
-      <c r="G17">
-        <v>250</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>1010</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <f t="shared" ref="A18:A33" si="2">ROW()-2+20000</f>
-        <v>20016</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>400</v>
-      </c>
-      <c r="G18">
-        <v>200</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>1010</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <f t="shared" si="2"/>
-        <v>20017</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>100</v>
-      </c>
-      <c r="G19">
-        <v>50</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>1010</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <f t="shared" si="2"/>
-        <v>20018</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>500</v>
-      </c>
-      <c r="G20">
-        <v>250</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>1010</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <f t="shared" si="2"/>
-        <v>20019</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1300</v>
-      </c>
-      <c r="G21">
-        <v>650</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>1010</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <f t="shared" si="2"/>
-        <v>20020</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>300</v>
-      </c>
-      <c r="G22">
-        <v>150</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>1010</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <f t="shared" si="2"/>
-        <v>20021</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>800</v>
-      </c>
-      <c r="G23">
-        <v>400</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>1010</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <f t="shared" si="2"/>
-        <v>20022</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>600</v>
-      </c>
-      <c r="G24">
-        <v>200</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>1010</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <f t="shared" si="2"/>
-        <v>20023</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>300</v>
-      </c>
-      <c r="G25">
-        <v>150</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>1010</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <f t="shared" si="2"/>
-        <v>20024</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>300</v>
-      </c>
-      <c r="G26">
-        <v>150</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>1010</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <f t="shared" si="2"/>
-        <v>20025</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>500</v>
-      </c>
-      <c r="G27">
-        <v>250</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>1010</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <f t="shared" si="2"/>
-        <v>20026</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>500</v>
-      </c>
-      <c r="G28">
-        <v>250</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>1010</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <f t="shared" si="2"/>
-        <v>20027</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>3000</v>
-      </c>
-      <c r="G29">
-        <v>1500</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>1010</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <f t="shared" si="2"/>
-        <v>20028</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>1000</v>
-      </c>
-      <c r="G30">
-        <v>500</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>1010</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <f t="shared" si="2"/>
-        <v>20029</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1200</v>
-      </c>
-      <c r="G31">
-        <v>600</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>1010</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <f t="shared" si="2"/>
-        <v>20030</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>500</v>
-      </c>
-      <c r="G32">
-        <v>250</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>1010</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <f t="shared" si="2"/>
-        <v>20031</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>3000</v>
-      </c>
-      <c r="G33">
-        <v>1500</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>1010</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
   <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -12063,13 +10948,1292 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f t="shared" ref="A2:A35" si="0">ROW()-2+30000</f>
-        <v>30000</v>
+        <f t="shared" ref="A2:A6" si="0">ROW()-2+20000</f>
+        <v>20000</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>171</v>
       </c>
       <c r="C2">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1010</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <f t="shared" si="0"/>
+        <v>20001</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1010</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>20002</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>70</v>
+      </c>
+      <c r="G4">
+        <v>35</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1010</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>20003</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1010</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>20004</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>45</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1010</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <f t="shared" ref="A7:A17" si="1">ROW()-2+20000</f>
+        <v>20005</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1010</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <f t="shared" si="1"/>
+        <v>20006</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1010</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <f t="shared" si="1"/>
+        <v>20007</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1010</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <f t="shared" si="1"/>
+        <v>20008</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1010</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f t="shared" si="1"/>
+        <v>20009</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>50</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1010</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <f t="shared" si="1"/>
+        <v>20010</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>2000</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1010</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <f t="shared" si="1"/>
+        <v>20011</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>2500</v>
+      </c>
+      <c r="G13">
+        <v>1250</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1010</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <f t="shared" si="1"/>
+        <v>20012</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1500</v>
+      </c>
+      <c r="G14">
+        <v>500</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1010</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <f t="shared" si="1"/>
+        <v>20013</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>500</v>
+      </c>
+      <c r="G15">
+        <v>250</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1010</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <f t="shared" si="1"/>
+        <v>20014</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>500</v>
+      </c>
+      <c r="G16">
+        <v>250</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1010</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f t="shared" si="1"/>
+        <v>20015</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>3000</v>
+      </c>
+      <c r="G17">
+        <v>250</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1010</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f t="shared" ref="A18:A35" si="2">ROW()-2+20000</f>
+        <v>20016</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>3000</v>
+      </c>
+      <c r="G18">
+        <v>1500</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1010</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f t="shared" si="2"/>
+        <v>20017</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>2500</v>
+      </c>
+      <c r="G19">
+        <v>1000</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1010</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f t="shared" si="2"/>
+        <v>20018</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>2000</v>
+      </c>
+      <c r="G20">
+        <v>1000</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1010</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f t="shared" si="2"/>
+        <v>20019</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>600</v>
+      </c>
+      <c r="G21">
+        <v>200</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1010</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <f t="shared" si="2"/>
+        <v>20020</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>400</v>
+      </c>
+      <c r="G22">
+        <v>200</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1010</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <f t="shared" si="2"/>
+        <v>20021</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>50</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1010</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <f t="shared" si="2"/>
+        <v>20022</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>500</v>
+      </c>
+      <c r="G24">
+        <v>250</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1010</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <f t="shared" si="2"/>
+        <v>20023</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>1300</v>
+      </c>
+      <c r="G25">
+        <v>650</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1010</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <f t="shared" si="2"/>
+        <v>20024</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>300</v>
+      </c>
+      <c r="G26">
+        <v>150</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1010</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f t="shared" si="2"/>
+        <v>20025</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>800</v>
+      </c>
+      <c r="G27">
+        <v>400</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1010</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f t="shared" si="2"/>
+        <v>20026</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>300</v>
+      </c>
+      <c r="G28">
+        <v>150</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1010</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <f t="shared" si="2"/>
+        <v>20027</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>300</v>
+      </c>
+      <c r="G29">
+        <v>150</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1010</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <f t="shared" si="2"/>
+        <v>20028</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>500</v>
+      </c>
+      <c r="G30">
+        <v>250</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1010</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <f t="shared" si="2"/>
+        <v>20029</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>500</v>
+      </c>
+      <c r="G31">
+        <v>250</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1010</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f t="shared" si="2"/>
+        <v>20030</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1000</v>
+      </c>
+      <c r="G32">
+        <v>500</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1010</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <f t="shared" si="2"/>
+        <v>20031</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1200</v>
+      </c>
+      <c r="G33">
+        <v>600</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1010</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <f t="shared" si="2"/>
+        <v>20032</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>500</v>
+      </c>
+      <c r="G34">
+        <v>250</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1010</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <f t="shared" si="2"/>
+        <v>20033</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>3000</v>
+      </c>
+      <c r="G35">
+        <v>1500</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1010</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6001720-9AA1-466F-8E06-D372A3A538C0}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <f t="shared" ref="A2:A37" si="0">ROW()-2+30000</f>
+        <v>30000</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2">
         <v>10</v>
       </c>
       <c r="D2">
@@ -12967,7 +13131,7 @@
         <v>30025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>236</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -12979,10 +13143,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="G27">
-        <v>125</v>
+        <v>1500</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -13003,7 +13167,7 @@
         <v>30026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -13015,10 +13179,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>300</v>
+        <v>5000</v>
       </c>
       <c r="G28">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -13039,7 +13203,7 @@
         <v>30027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -13051,10 +13215,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -13075,7 +13239,7 @@
         <v>30028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -13087,10 +13251,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="G30">
-        <v>5000</v>
+        <v>150</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -13111,7 +13275,7 @@
         <v>30029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -13123,13 +13287,13 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="G31">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -13147,7 +13311,7 @@
         <v>30030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -13159,13 +13323,13 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="G32">
-        <v>250</v>
+        <v>5000</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -13183,7 +13347,7 @@
         <v>30031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -13195,13 +13359,13 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G33">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -13219,7 +13383,7 @@
         <v>30032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -13231,13 +13395,13 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G34">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -13255,7 +13419,7 @@
         <v>30033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>183</v>
+        <v>95</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -13267,13 +13431,13 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>2800</v>
+        <v>500</v>
       </c>
       <c r="G35">
-        <v>1400</v>
+        <v>250</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -13282,6 +13446,78 @@
         <v>1020</v>
       </c>
       <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>30034</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>700</v>
+      </c>
+      <c r="G36">
+        <v>350</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1020</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>30035</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>2800</v>
+      </c>
+      <c r="G37">
+        <v>1400</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1020</v>
+      </c>
+      <c r="K37">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A3DD8E-4A56-4FB0-9011-BBF69E1994AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF51D50-3938-4706-A768-8E8F577DE227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="735" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1935" yWindow="1275" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="239">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -987,6 +987,10 @@
   </si>
   <si>
     <t>mg_caramelized_book</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>confiserie_recipi</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10900,7 +10904,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11524,7 +11528,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" ref="A18:A35" si="2">ROW()-2+20000</f>
+        <f t="shared" ref="A18:A36" si="2">ROW()-2+20000</f>
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -11582,7 +11586,7 @@
         <v>1000</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -11744,7 +11748,7 @@
         <v>20022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -11756,10 +11760,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G24">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -11780,7 +11784,7 @@
         <v>20023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -11792,10 +11796,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="G25">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -11816,7 +11820,7 @@
         <v>20024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -11828,10 +11832,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="G26">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -11852,7 +11856,7 @@
         <v>20025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -11864,10 +11868,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G27">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -11888,7 +11892,7 @@
         <v>20026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -11900,10 +11904,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="G28">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -11924,7 +11928,7 @@
         <v>20027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -11942,7 +11946,7 @@
         <v>150</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -11960,7 +11964,7 @@
         <v>20028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -11972,10 +11976,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G30">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -11996,7 +12000,7 @@
         <v>20029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -12032,7 +12036,7 @@
         <v>20030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -12044,10 +12048,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G32">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -12068,7 +12072,7 @@
         <v>20031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -12080,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="G33">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -12104,7 +12108,7 @@
         <v>20032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -12116,10 +12120,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="G34">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -12140,7 +12144,7 @@
         <v>20033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -12152,10 +12156,10 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G35">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -12167,6 +12171,42 @@
         <v>1010</v>
       </c>
       <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <f t="shared" si="2"/>
+        <v>20034</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>3000</v>
+      </c>
+      <c r="G36">
+        <v>1500</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1010</v>
+      </c>
+      <c r="K36">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF51D50-3938-4706-A768-8E8F577DE227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6948C369-33D2-4050-9205-5D4C80E3AEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="1275" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -6148,7 +6148,7 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6948C369-33D2-4050-9205-5D4C80E3AEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3B3551-35A5-42E7-AA7A-63FCCE137CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1230" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -6256,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3B3551-35A5-42E7-AA7A-63FCCE137CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90487AF-6CFB-4F6C-96EA-06285859DD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1230" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="1095" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="239">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -10904,7 +10904,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F083EA-800F-48D3-B24D-32DC46FC256B}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -11528,7 +11528,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" ref="A18:A36" si="2">ROW()-2+20000</f>
+        <f t="shared" ref="A18:A37" si="2">ROW()-2+20000</f>
         <v>20016</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -11604,7 +11604,7 @@
         <v>20018</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -11616,10 +11616,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -11640,7 +11640,7 @@
         <v>20019</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G21">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -11676,7 +11676,7 @@
         <v>20020</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G22">
         <v>200</v>
@@ -11712,7 +11712,7 @@
         <v>20021</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -11724,10 +11724,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="G23">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -11748,7 +11748,7 @@
         <v>20022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>238</v>
+        <v>179</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -11760,10 +11760,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G24">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -11784,7 +11784,7 @@
         <v>20023</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>238</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -11796,10 +11796,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G25">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -11820,7 +11820,7 @@
         <v>20024</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -11832,10 +11832,10 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="G26">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -11856,7 +11856,7 @@
         <v>20025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -11868,10 +11868,10 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="G27">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -11892,7 +11892,7 @@
         <v>20026</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -11904,10 +11904,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G28">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -11928,7 +11928,7 @@
         <v>20027</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -11940,10 +11940,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="G29">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -11964,7 +11964,7 @@
         <v>20028</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -11982,7 +11982,7 @@
         <v>150</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -12000,7 +12000,7 @@
         <v>20029</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -12012,10 +12012,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G31">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -12036,7 +12036,7 @@
         <v>20030</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -12072,7 +12072,7 @@
         <v>20031</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G33">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -12108,7 +12108,7 @@
         <v>20032</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -12120,10 +12120,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="G34">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -12144,7 +12144,7 @@
         <v>20033</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -12156,10 +12156,10 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="G35">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -12180,7 +12180,7 @@
         <v>20034</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -12192,10 +12192,10 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G36">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -12207,6 +12207,42 @@
         <v>1010</v>
       </c>
       <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <f t="shared" si="2"/>
+        <v>20035</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>3000</v>
+      </c>
+      <c r="G37">
+        <v>1500</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1010</v>
+      </c>
+      <c r="K37">
         <v>1</v>
       </c>
     </row>
@@ -13219,10 +13255,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G28">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="H28">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_shopItemDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90487AF-6CFB-4F6C-96EA-06285859DD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D985E09-09F3-4E25-A735-6AD76EA0C6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="1095" windowWidth="25005" windowHeight="14370" tabRatio="804" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="1065" windowWidth="25005" windowHeight="14355" tabRatio="804" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemDB_1" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="240">
   <si>
     <t>butter</t>
     <phoneticPr fontId="1"/>
@@ -991,6 +991,10 @@
   </si>
   <si>
     <t>confiserie_recipi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>red_jemstone</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5143,7 +5147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F419484-2581-4537-A85C-9AB9116FDAC4}">
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5226,7 +5230,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A84" si="0">ROW()-2+2000</f>
+        <f t="shared" ref="A3:A85" si="0">ROW()-2+2000</f>
         <v>2001</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7030,10 +7034,10 @@
         <v>2051</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D53">
         <v>6</v>
@@ -7042,13 +7046,13 @@
         <v>1</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -7066,7 +7070,7 @@
         <v>2052</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -7075,13 +7079,13 @@
         <v>6</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -7102,7 +7106,7 @@
         <v>2053</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -7138,7 +7142,7 @@
         <v>2054</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -7174,7 +7178,7 @@
         <v>2055</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -7210,7 +7214,7 @@
         <v>2056</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7246,7 +7250,7 @@
         <v>2057</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -7282,7 +7286,7 @@
         <v>2058</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7318,7 +7322,7 @@
         <v>2059</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -7354,7 +7358,7 @@
         <v>2060</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -7390,7 +7394,7 @@
         <v>2061</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -7426,7 +7430,7 @@
         <v>2062</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -7462,7 +7466,7 @@
         <v>2063</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -7498,7 +7502,7 @@
         <v>2064</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7534,7 +7538,7 @@
         <v>2065</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>233</v>
+        <v>137</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7543,16 +7547,16 @@
         <v>6</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="b">
         <v>0</v>
@@ -7570,7 +7574,7 @@
         <v>2066</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7579,16 +7583,16 @@
         <v>6</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H68">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -7606,7 +7610,7 @@
         <v>2067</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7615,13 +7619,13 @@
         <v>6</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H69">
         <v>2000</v>
@@ -7642,7 +7646,7 @@
         <v>2068</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7654,7 +7658,7 @@
         <v>1</v>
       </c>
       <c r="F70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70">
         <v>2</v>
@@ -7678,7 +7682,7 @@
         <v>2069</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7690,10 +7694,10 @@
         <v>1</v>
       </c>
       <c r="F71">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H71">
         <v>2000</v>
@@ -7714,7 +7718,7 @@
         <v>2070</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7726,13 +7730,13 @@
         <v>1</v>
       </c>
       <c r="F72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I72" t="b">
         <v>0</v>
@@ -7750,7 +7754,7 @@
         <v>2071</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7762,10 +7766,10 @@
         <v>1</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -7786,7 +7790,7 @@
         <v>2072</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7804,7 +7808,7 @@
         <v>2</v>
       </c>
       <c r="H74">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -7822,7 +7826,7 @@
         <v>2073</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7834,10 +7838,10 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>2000</v>
@@ -7858,7 +7862,7 @@
         <v>2074</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7867,16 +7871,16 @@
         <v>6</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76">
+        <v>10</v>
+      </c>
+      <c r="G76">
         <v>5</v>
       </c>
-      <c r="G76">
-        <v>2</v>
-      </c>
       <c r="H76">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
@@ -7894,7 +7898,7 @@
         <v>2075</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7930,7 +7934,7 @@
         <v>2076</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7942,13 +7946,13 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -7966,7 +7970,7 @@
         <v>2077</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7978,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79">
         <v>2000</v>
@@ -8002,7 +8006,7 @@
         <v>2078</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -8014,10 +8018,10 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80">
         <v>2000</v>
@@ -8038,7 +8042,7 @@
         <v>2079</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -8074,7 +8078,7 @@
         <v>2080</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>228</v>
+        <v>148</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -8086,10 +8090,10 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>2000</v>
@@ -8110,7 +8114,7 @@
         <v>2081</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -8122,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83">
         <v>2000</v>
@@ -8146,7 +8150,7 @@
         <v>2082</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -8158,10 +8162,10 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84">
         <v>2000</v>
@@ -8173,6 +8177,42 @@
         <v>100</v>
       </c>
       <c r="K84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <f t="shared" si="0"/>
+        <v>2083</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <v>6</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>6</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="H85">
+        <v>2000</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>100</v>
+      </c>
+      <c r="K85">
         <v>1</v>
       </c>
     </row>
